--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,19 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,13 +69,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF6B6B"/>
+      <color rgb="0053D769"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0053D769"/>
+      <color rgb="00FF6B6B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -168,13 +169,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -545,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -605,168 +606,190 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -777,7 +800,480 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Development Timeline</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>What landed when (derived from source history)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Work landed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>v1.0 baseline: engine + UI (Main, MainComponent, ControlPanel, InfoPanel, RadiationPatternComponent, AcousticEngine, ColourMaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Measured-directivity loading added (MeasurementData)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>v1.1 theming foundation: theme-aware palette + AtomikLookAndFeel (BrandTheme)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Preferences/settings, .atmk projects + dashboard, enhanced heatmap export, PDF pipeline, grid + CAD/DXF, array presets, app icon + installer, header responsiveness, version bump, red-&gt;cyan overhaul</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Window scaling (min size, fixed aspect ratio, clamps); fresh-install guarantee; Recent Projects hygiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Dual measurement datasets (Ground Plane / Room), selectable + separate; final naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>PS-001…PS-019: 1/3-octave freqs, Ground Plane-only UI, XN18-n, -6 dB legend, PDF/CSV/PNG polish, Set to Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>prediction-software repo initial commit (Q21S / XN18 tree)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Plot drawing tools + BEM/directivity math (633fc36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-07 (approx)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>v1.2.x beta UI redesign (Graph colors.pdf → betav1.2.3 packaging)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>v1.3.0 Windows build: Atomik Simulation Engine rename, ATOMIK-only logo, header v1.3.0 fix, Ctrl+Z/Y, Statistics button, single Release exe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Q21S BEM polar×1/r, cardioid, cabinet size, heatmap docs, version archive; plot shapes + opacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Windows Q21S data-path fix + portable ZIP (EXE+MeasurementIntegrationPack); archive Windows = ZIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.3.8  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04  |  Command line aliases + typed points + MOVE/ZOOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Command registry</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Short form and full name share one handler (L/LINE, PE/PENCIL, SPK/ADDSPEAKER, …)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Typed-point DRAW</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>After LINE/CIRCLE/… enter x,y (metres) or click the plot</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>MOVE / ZOOM sessions</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>MOVE base/second point; ZOOM [Extents/In/Out]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Dock / Undock</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Floating terminal window; state remembered</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>HELP / ?</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Atomik-branded command list (no third-party CAD branding)</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Undocked Esc / finish</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Completing or cancelling a command no longer loses the floating terminal</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Version → v1.3.8</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App, resource, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -840,7 +1336,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -867,7 +1363,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -894,7 +1390,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -921,7 +1417,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -948,7 +1444,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -975,7 +1471,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1002,7 +1498,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1056,7 +1552,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1113,7 +1609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1176,7 +1672,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1203,7 +1699,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1230,7 +1726,7 @@
           <t>Docs</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1287,7 +1783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1350,7 +1846,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1377,7 +1873,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1404,7 +1900,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1431,7 +1927,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1458,7 +1954,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1485,7 +1981,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1512,7 +2008,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1542,7 +2038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1620,7 +2116,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1647,7 +2143,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1674,7 +2170,7 @@
           <t>Docs / pack</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1701,7 +2197,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1728,7 +2224,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1755,7 +2251,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1782,7 +2278,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1809,7 +2305,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1836,7 +2332,7 @@
           <t>Editing</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1863,7 +2359,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1890,7 +2386,7 @@
           <t>DSP / UI (PS batch)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1944,7 +2440,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1998,7 +2494,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2052,7 +2548,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2106,7 +2602,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2160,7 +2656,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2187,7 +2683,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2214,7 +2710,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2241,7 +2737,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2268,7 +2764,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2313,7 +2809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2376,7 +2872,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2430,7 +2926,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2484,7 +2980,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2515,7 +3011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2593,7 +3089,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2620,7 +3116,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2647,7 +3143,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2674,7 +3170,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2701,7 +3197,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2728,7 +3224,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2755,7 +3251,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2782,7 +3278,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2809,7 +3305,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2836,7 +3332,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2863,7 +3359,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2890,7 +3386,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2917,7 +3413,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2944,7 +3440,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2971,7 +3467,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2998,7 +3494,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3025,7 +3521,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3052,7 +3548,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3079,7 +3575,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3106,7 +3602,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3133,7 +3629,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3160,7 +3656,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3187,7 +3683,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3214,7 +3710,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3241,7 +3737,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3268,7 +3764,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3295,7 +3791,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3349,7 +3845,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3403,7 +3899,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3430,7 +3926,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3457,7 +3953,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3484,7 +3980,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3511,7 +4007,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3556,7 +4052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3748,222 +4244,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Development Timeline</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>What landed when (derived from source history)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Work landed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>v1.0 baseline: engine + UI (Main, MainComponent, ControlPanel, InfoPanel, RadiationPatternComponent, AcousticEngine, ColourMaps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Measured-directivity loading added (MeasurementData)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>v1.1 theming foundation: theme-aware palette + AtomikLookAndFeel (BrandTheme)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Preferences/settings, .atmk projects + dashboard, enhanced heatmap export, PDF pipeline, grid + CAD/DXF, array presets, app icon + installer, header responsiveness, version bump, red-&gt;cyan overhaul</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Window scaling (min size, fixed aspect ratio, clamps); fresh-install guarantee; Recent Projects hygiene</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Dual measurement datasets (Ground Plane / Room), selectable + separate; final naming</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>PS-001…PS-019: 1/3-octave freqs, Ground Plane-only UI, XN18-n, -6 dB legend, PDF/CSV/PNG polish, Set to Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>prediction-software repo initial commit (Q21S / XN18 tree)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Plot drawing tools + BEM/directivity math (633fc36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07 (approx)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>v1.2.x beta UI redesign (Graph colors.pdf → betav1.2.3 packaging)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>v1.3.0 Windows build: Atomik Simulation Engine rename, ATOMIK-only logo, header v1.3.0 fix, Ctrl+Z/Y, Statistics button, single Release exe</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Q21S BEM polar×1/r, cardioid, cabinet size, heatmap docs, version archive; plot shapes + opacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Windows Q21S data-path fix + portable ZIP (EXE+MeasurementIntegrationPack); archive Windows = ZIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,20 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,13 +76,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF6B6B"/>
+      <color rgb="0044D9E6"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0044D9E6"/>
+      <color rgb="00FF6B6B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -172,13 +173,13 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -606,190 +607,234 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>1.2.x</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Beta UI redesign (betav1.2.3)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -806,6 +851,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.0.0  -  Initial Baseline</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22  (measured directivity added 2026-06-24)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>View modes</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>SPL Heatmap, Pressure Map, Interference, Directivity, Measured Polar, Fit View</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Acoustic metrics</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>SPL, Frequency Response, RT60, Absorption, Transmission Loss, heatmaps</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Frequency selector</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>20, 30, 40, 50, 60, 70, 80, 90, 100, 110, 120, 150, 200, 500 Hz</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Measured directivity</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Horizontal directivity from .xlsx; applied when sim frequency matches; 1/3-octave smoothing; optional 3 dB contour bands</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Speaker / scene controls</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Per-unit X/Y, gain (dB), delay (ms), invert polarity, reverse orientation, enable/disable; add/delete; quick layouts (1/2/3 devices)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Simulation settings</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Grid resolution, dB floor</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Exports</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>PNG image, CSV data, SVG figure</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Monopole summation + frequency-dependent piston directivity fallback; fractional-octave band power averaging</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Branding &amp; UI</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>JUCE desktop app; Montserrat + Space Mono fonts; Atomik identity</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1019,6 +1258,504 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18  |  Figma UI cut + square full-bleed grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Branding</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ATOMIK. wordmark</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>New horizontal logo (with trailing dot) at Figma size/position; light and dark ink variants generated from the source art</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Ribbon</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Snap / Ortho slot</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Laid out after Help, captioned and divided like every other cluster, behind kShowOptionsCluster (off). Ctrl+F and the SNAP / ORTHO verbs stay live</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Info panel</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Replaces the stock message box for the info and ? popups: no icon disc, no OK button, red close cross top-right</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Heatmap -&gt; Gradient Plot</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Canvas caption, stats chip, terminal VIEWSPL, PDF report title and rows, tooltips</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Square, full-bleed grid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Uniform px/m so cells are square; the grid rules the whole canvas rather than stopping at the field edge, and the field's floor tone fills the surround</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Contrast-aware axis numbers</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>White with a halo over a rendered field, theme ink over the bare grid; colliding tick labels are skipped</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Canvas caption ink</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Brand red on the empty grid, white once a device is placed</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sidebar tracks window width</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Holds the design's 17.7% share at any aspect (was 13.3% at 21:9, 12.4% at 4K)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Scale ceiling 1.85 -&gt; 2.70</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>A 4K client area needs 2.63 and was clamped, rendering every band ~30% thinner than its share of the screen</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Vertical centring</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Run info, export buttons and the status pill centred in their rows</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Dark theme hidden</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Light theme only for this release; code intact</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Icons shrank on units / theme switch</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Ribbon</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Icons rendered as black squares</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Rel. SPL bar overlapped the plot</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Contour bands collapsed below -18 dB</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1216,7 +1953,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1273,7 +2010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1336,7 +2073,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1363,7 +2100,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1390,7 +2127,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1417,7 +2154,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1525,7 +2262,7 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1579,7 +2316,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1609,7 +2346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1672,7 +2409,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1699,7 +2436,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1753,7 +2490,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1783,7 +2520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2038,7 +2775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2413,7 +3150,7 @@
           <t>Cabinet</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2467,7 +3204,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2521,7 +3258,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2575,7 +3312,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2629,7 +3366,7 @@
           <t>DSP</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2683,7 +3420,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2710,7 +3447,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2737,7 +3474,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2764,7 +3501,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2809,7 +3546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2899,7 +3636,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2953,7 +3690,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3011,7 +3748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3818,7 +4555,7 @@
           <t>Versioning</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3872,7 +4609,7 @@
           <t>Measured directivity</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3926,7 +4663,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3953,7 +4690,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3980,7 +4717,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4007,7 +4744,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4050,198 +4787,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.0.0  -  Initial Baseline</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-22  (measured directivity added 2026-06-24)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>View modes</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>SPL Heatmap, Pressure Map, Interference, Directivity, Measured Polar, Fit View</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Acoustic metrics</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>SPL, Frequency Response, RT60, Absorption, Transmission Loss, heatmaps</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Frequency selector</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>20, 30, 40, 50, 60, 70, 80, 90, 100, 110, 120, 150, 200, 500 Hz</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Measured directivity</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Horizontal directivity from .xlsx; applied when sim frequency matches; 1/3-octave smoothing; optional 3 dB contour bands</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Speaker / scene controls</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Per-unit X/Y, gain (dB), delay (ms), invert polarity, reverse orientation, enable/disable; add/delete; quick layouts (1/2/3 devices)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Simulation settings</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Grid resolution, dB floor</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Exports</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>PNG image, CSV data, SVG figure</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Monopole summation + frequency-dependent piston directivity fallback; fractional-octave band power averaging</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Branding &amp; UI</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>JUCE desktop app; Montserrat + Space Mono fonts; Atomik identity</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1725,22 +1725,49 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Assets embedded in the EXE</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Square, full-bleed grid</t>
+          <t>Field stretched to fill the canvas</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Uniform px/m so cells are square; the grid rules the whole canvas rather than stopping at the field edge, and the field's floor tone fills the surround</t>
+          <t>Whole 100 x 100 m world visible edge to edge, and the visible grid is exactly the simulated area so units place anywhere grid is drawn. Cells are rectangles on a non-square window</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1614,7 +1614,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Icons shrank on units / theme switch</t>
+          <t>Prediction fell back to omni off-machine</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
+          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Icons rendered as black squares</t>
+          <t>Speaker markers elongated</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
+          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Rel. SPL bar overlapped the plot</t>
+          <t>Icons shrank on units / theme switch</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Contour bands collapsed below -18 dB</t>
+          <t>Icons rendered as black squares</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Legend</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Assets embedded in the EXE</t>
+          <t>Rel. SPL bar overlapped the plot</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+          <t>Anchored to the gutter's left edge instead of right-anchored</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1749,25 +1749,79 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Contour bands collapsed below -18 dB</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Assets embedded in the EXE</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Field stretched to fill the canvas</t>
+          <t>Drawn to scale (square grid)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Whole 100 x 100 m world visible edge to edge, and the visible grid is exactly the simulated area so units place anywhere grid is drawn. Cells are rectangles on a non-square window</t>
+          <t>One px/m on both axes so the square 100 x 100 m world renders square and cells are square in every window; grid is still exactly the simulated area. Margins appear on one axis</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1452,22 +1452,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Contrast-aware axis numbers</t>
+          <t>Q21S dimensions corrected</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>White with a halo over a rendered field, theme ink over the bare grid; colliding tick labels are skipped</t>
+          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m, so the marker is to scale and the 1/r floor follows the true depth</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Canvas caption ink</t>
+          <t>Contrast-aware axis numbers</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Brand red on the empty grid, white once a device is placed</t>
+          <t>White with a halo over a rendered field, theme ink over the bare grid; colliding tick labels are skipped</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sidebar tracks window width</t>
+          <t>Canvas caption ink</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Holds the design's 17.7% share at any aspect (was 13.3% at 21:9, 12.4% at 4K)</t>
+          <t>Brand red on the empty grid, white once a device is placed</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Scale ceiling 1.85 -&gt; 2.70</t>
+          <t>Sidebar tracks window width</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>A 4K client area needs 2.63 and was clamped, rendering every band ~30% thinner than its share of the screen</t>
+          <t>Holds the design's 17.7% share at any aspect (was 13.3% at 21:9, 12.4% at 4K)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Vertical centring</t>
+          <t>Scale ceiling 1.85 -&gt; 2.70</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Run info, export buttons and the status pill centred in their rows</t>
+          <t>A 4K client area needs 2.63 and was clamped, rendering every band ~30% thinner than its share of the screen</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Dark theme hidden</t>
+          <t>Vertical centring</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Light theme only for this release; code intact</t>
+          <t>Run info, export buttons and the status pill centred in their rows</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1614,22 +1614,22 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Measurements</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Prediction fell back to omni off-machine</t>
+          <t>Dark theme hidden</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
+          <t>Light theme only for this release; code intact</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Speaker markers elongated</t>
+          <t>Prediction fell back to omni off-machine</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
+          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Icons shrank on units / theme switch</t>
+          <t>Speaker markers elongated</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
+          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Icons rendered as black squares</t>
+          <t>Icons shrank on units / theme switch</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
+          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Rel. SPL bar overlapped the plot</t>
+          <t>Icons rendered as black squares</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Legend</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Contour bands collapsed below -18 dB</t>
+          <t>Rel. SPL bar overlapped the plot</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+          <t>Anchored to the gutter's left edge instead of right-anchored</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Assets embedded in the EXE</t>
+          <t>Contour bands collapsed below -18 dB</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1806,22 +1806,49 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Assets embedded in the EXE</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Drawn to scale (square grid)</t>
+          <t>Drawn to scale, full bleed</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>One px/m on both axes so the square 100 x 100 m world renders square and cells are square in every window; grid is still exactly the simulated area. Margins appear on one axis</t>
+          <t>One px/m on both axes so cells are square in every window, and the fit fills the canvas edge to edge. Crops the shorter axis; zoom-out past the fit now reaches the whole field</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Drawn to scale, full bleed</t>
+          <t>Simulated region follows the view</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>One px/m on both axes so cells are square in every window, and the fit fills the canvas edge to edge. Crops the shorter axis; zoom-out past the fit now reaches the whole field</t>
+          <t>The fixed 100 x 100 m world is gone: the plot asks for a region shaped to its own aspect, so the field covers the canvas exactly with square cells, and zoom changes how many metres are solved rather than cropping a box (2 m - 20 km)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Q21S dimensions corrected</t>
+          <t>X / Y sliders capped at 100 m</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m, so the marker is to scale and the 1/r floor follows the true depth</t>
+          <t>Spans were hard-coded 0..100 m and silently clamped every unit to the old box; they now follow the simulated region</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1479,22 +1479,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Contrast-aware axis numbers</t>
+          <t>Q21S dimensions corrected</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>White with a halo over a rendered field, theme ink over the bare grid; colliding tick labels are skipped</t>
+          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m, so the marker is to scale and the 1/r floor follows the true depth</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Canvas caption ink</t>
+          <t>Contrast-aware axis numbers</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Brand red on the empty grid, white once a device is placed</t>
+          <t>White with a halo over a rendered field, theme ink over the bare grid; colliding tick labels are skipped</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Sidebar tracks window width</t>
+          <t>Canvas caption ink</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Holds the design's 17.7% share at any aspect (was 13.3% at 21:9, 12.4% at 4K)</t>
+          <t>Brand red on the empty grid, white once a device is placed</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Scale ceiling 1.85 -&gt; 2.70</t>
+          <t>Sidebar tracks window width</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>A 4K client area needs 2.63 and was clamped, rendering every band ~30% thinner than its share of the screen</t>
+          <t>Holds the design's 17.7% share at any aspect (was 13.3% at 21:9, 12.4% at 4K)</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Vertical centring</t>
+          <t>Scale ceiling 1.85 -&gt; 2.70</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Run info, export buttons and the status pill centred in their rows</t>
+          <t>A 4K client area needs 2.63 and was clamped, rendering every band ~30% thinner than its share of the screen</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Dark theme hidden</t>
+          <t>Vertical centring</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Light theme only for this release; code intact</t>
+          <t>Run info, export buttons and the status pill centred in their rows</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1641,22 +1641,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Measurements</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Prediction fell back to omni off-machine</t>
+          <t>Dark theme hidden</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
+          <t>Light theme only for this release; code intact</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Speaker markers elongated</t>
+          <t>Prediction fell back to omni off-machine</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
+          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Icons shrank on units / theme switch</t>
+          <t>Speaker markers elongated</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
+          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Icons rendered as black squares</t>
+          <t>Icons shrank on units / theme switch</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
+          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Rel. SPL bar overlapped the plot</t>
+          <t>Icons rendered as black squares</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Legend</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Contour bands collapsed below -18 dB</t>
+          <t>Rel. SPL bar overlapped the plot</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+          <t>Anchored to the gutter's left edge instead of right-anchored</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Assets embedded in the EXE</t>
+          <t>Contour bands collapsed below -18 dB</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1833,22 +1833,49 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Assets embedded in the EXE</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1668,7 +1668,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Prediction fell back to omni off-machine</t>
+          <t>Pan did nothing</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
+          <t>The solved region fills the view, so clampViewToField pinned the offset back to zero every drag. Panning now moves the region itself; middle-drag pans from any tool</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Speaker markers elongated</t>
+          <t>Zoom anchored on the region corner</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
+          <t>Zooming in walked off into empty space; it now keeps the view centre</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Icons shrank on units / theme switch</t>
+          <t>SPL caption sat mid-canvas</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
+          <t>Was inset to the field's left edge, left over from the letterboxed view</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Icons rendered as black squares</t>
+          <t>Prediction fell back to omni off-machine</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
+          <t>A stored measurementSource of 1 selected a non-existent combo id (blank control) and pointed at a sidecar shyamGuildMeasurements folder shipped builds lack, so the engine lost Q21S directivity. Source is validated; combo never blanks</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Plot</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Rel. SPL bar overlapped the plot</t>
+          <t>Speaker markers elongated</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+          <t>Cabinet footprint inherited the view's anisotropy (3.33:1 vs a true 1.22:1 plan ratio); the glyph is now sized from a single px/m</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Contour bands collapsed below -18 dB</t>
+          <t>Icons shrank on units / theme switch</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+          <t>Header restyle stamped its own inset onto the ribbon's adopted glyphs, and JUCE skips resized() when bounds do not change</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Assets embedded in the EXE</t>
+          <t>Icons rendered as black squares</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+          <t>Figma SVGs wrap base64 bitmaps in a pattern fill JUCE cannot render; bitmaps extracted and preferred as PNG</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -1857,25 +1857,106 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Rel. SPL bar overlapped the plot</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Anchored to the gutter's left edge instead of right-anchored</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Contour bands collapsed below -18 dB</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>splBand quantizes the gradient instead of indexing a 7-entry palette that ran out at the UI's 3 dB step</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Assets embedded in the EXE</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Logos, ribbon icons and bundled fonts baked in by Tools/embed_assets.py. They were read from an Assets/ folder found by walking up from the CWD or EXE, so a recipient of just the .exe saw no logo, no glyphs and fallback fonts</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,21 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -167,19 +168,19 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -547,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -607,7 +608,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -617,224 +618,246 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -851,6 +874,1047 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.1.0  -  Detailed Changes</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Development window 2026-06-25 -&gt; 2026-06-29</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Theming &amp; Preferences</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Dark / Light themes</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic app-wide switching via theme-aware palette + AtomikLookAndFeel; every screen/graph/dialog/heatmap chrome adapts live</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Theming &amp; Preferences</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Preferences / Settings tab</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Choose theme and unit system (SI / Imperial); displayed values convert, internal calcs stay SI</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Theming &amp; Preferences</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Persistent preferences</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Theme, units, grid visibility, measurement set, recent projects stored via PropertiesFile; broadcast via ChangeBroadcaster</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Project Workflow</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Project Dashboard at launch</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Separate window: new / open / recent projects; then opens main simulation window</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Project Workflow</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Project metadata capture</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Name, Engineer, Owner, Address, City, Country, Email, Mobile, Date - used in exports/reports</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Project Workflow</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Single-file .atmk projects</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Self-contained JSON: metadata + scene (speakers) + simulation settings; save/open</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Heatmap Export</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Client-ready heatmap sheet</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Header (logo, software name, title), project details, heatmap data (frequency, scale, units, legend) - generation logic untouched</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>PDF Report</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Multi-page PDF report</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Cover, Project Info, Input Parameters, Results, Graphs, Heatmaps (30/50/80/100 Hz), Summary - generated programmatically</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>PDF Report</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Custom PDF 1.4 writer (PdfDocument)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Vector text + embedded images, no external dependency</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>PDF Report</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>AcousticAnalysis module</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>RT60 (Sabine), absorption, transmission loss (mass-law), frequency response sampled from engine</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PDF Report</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>GraphRender</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Line/bar charts rendered to images for the report</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Workspace / Grid / Layout</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Improved grid</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Major/minor lines, zoom-adaptive spacing (niceStep), higher contrast; show/hide toggle (persisted)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Workspace / Grid / Layout</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Layout reference import</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Floor plans as background references - images (PNG/JPG) and DXF drawings</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Workspace / Grid / Layout</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>DXF parser (DxfImport)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Dependency-free 2D parser: LINE, LWPOLYLINE, POLYLINE/VERTEX, CIRCLE, ARC</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Workspace / Grid / Layout</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Layout alignment &amp; visibility tools</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Move, rotate, scale (width in m), opacity, show/hide, lock, snap-to-grid; live drag</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Array Presets</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Cardioid presets (2/3/4 sub)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Ready-to-use cardioid subwoofer arrays</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Array Presets</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>End-fired presets (2/3/4 sub)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Auto-calculated spacing, delay, polarity, orientation; manually editable after placement</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Measurement Datasets</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Two selectable sets (kept separate)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Ground Plane = factory open-field (30/60/100/150/200 Hz, 1 m); Room = GYLT (30/80/200/500 Hz, 0.5/1 m)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Measurement Datasets</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Per-set heatmaps &amp; polar plots</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Switching reloads only that dataset + rebuilds directivity; each polar normalised to its own on-axis level; selection persisted</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Measurement Datasets</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic availability/legend</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Measured-polar 'available frequencies' and legend generated from the loaded dataset</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Minimum window size</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Main 1120x686, dashboard 680x537 - layout can never collapse/hide controls</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Fixed widescreen aspect ratio</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>1340:820 preserved during resize - no stretching distortion</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Defensive layout clamps</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Workspace visible (P1), side panels usable (P2), controls keep usable size (P3)</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Scrollable control panel</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Dense controls scroll (viewport) instead of shrinking</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Responsive header + 'more options' menu</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Title auto-shrinks/never clips; Export PDF / Save / Preferences fold into kebab menu at all sizes</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Branding &amp; Installer</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Atomik app icon embedded</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Windows .rc icon for exe, installer wizard, Add/Remove Programs, shortcuts; generated by make_icon.py</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Branding &amp; Installer</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Windows installer (Inno Setup)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Single Setup.exe: app + both datasets + fonts + icon; static CRT (no VC++ redist); per-user; uninstaller</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Versioning</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>1.0.0 -&gt; 1.1.0</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>App title shows v1.1; installer 1.1</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Color system</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Removed all red; cyan accent system</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Header red-&gt;near-white; accents red-&gt;grey-&gt;cyan; hierarchy headings #F5F7FA / labels #B8C0CC / muted #7E8794; bg #0D0D12 / panel #17171D; accent #44D9E6; success #53D769; warning #FF6B6B; PDF FR line red-&gt;steel-blue</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Measured directivity</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Data-driven normalisation</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Each curve normalised to its own on-axis level instead of hard-coded reference SPLs</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Measurement Datasets</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Option renames</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Open Field -&gt; Ground Plane; GYLT -&gt; Room (datasets unchanged)</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Buttons no longer overlap title</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Fixed overlap in narrow/short windows</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Title no longer clips</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Was showing 'v1.' instead of 'v1.1'</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Recent Projects</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Recent Projects hygiene</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Entries whose .atmk no longer exists are hidden and pruned automatically</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Installer</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Fresh install guarantee</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Per-user settings folder cleared on install + uninstall; no stale recent projects/settings on reinstall</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E39"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1039,7 +2103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1258,6 +2322,261 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.1  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18  |  No letterboxing + pan + true Q21S size</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Middle-drag pans from any tool</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>No need to leave the tool you are drawing with</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Never letterboxes</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>The fill-the-canvas fit is the zoom floor, so no pale margins at any zoom. Field stays 100 x 100 m with square cells; the cropped band is reached by panning</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Q21S dimensions corrected</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m and the 1/r floor follows the true depth</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SPL caption back at the canvas edge</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Was inset to the field's left edge, left over from a letterboxed view</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Pan did nothing</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Zoom anchored on the field corner</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.1</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1347,7 +2666,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1401,7 +2720,7 @@
           <t>Naming</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1428,7 +2747,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1482,7 +2801,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1509,7 +2828,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1536,7 +2855,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1563,7 +2882,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1590,7 +2909,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1617,7 +2936,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1644,7 +2963,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1698,7 +3017,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1752,7 +3071,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1806,7 +3125,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1860,7 +3179,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1914,7 +3233,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1941,7 +3260,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1971,7 +3290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2061,7 +3380,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2115,7 +3434,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2196,7 +3515,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2226,7 +3545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2289,7 +3608,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2343,7 +3662,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2424,7 +3743,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2451,7 +3770,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2478,7 +3797,7 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2505,7 +3824,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2532,7 +3851,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2562,7 +3881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2625,7 +3944,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2706,7 +4025,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2736,7 +4055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2826,7 +4145,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2880,7 +4199,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2934,7 +4253,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2961,7 +4280,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2991,7 +4310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3096,7 +4415,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3150,7 +4469,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3204,7 +4523,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3258,7 +4577,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3312,7 +4631,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3366,7 +4685,7 @@
           <t>Cabinet</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3393,7 +4712,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3420,7 +4739,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3447,7 +4766,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3474,7 +4793,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3501,7 +4820,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3528,7 +4847,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3555,7 +4874,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3582,7 +4901,7 @@
           <t>DSP</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3609,7 +4928,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3663,7 +4982,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3717,7 +5036,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3762,7 +5081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3825,7 +5144,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3852,7 +5171,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3879,7 +5198,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3906,7 +5225,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3962,1045 +5281,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.1.0  -  Detailed Changes</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Development window 2026-06-25 -&gt; 2026-06-29</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Theming &amp; Preferences</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Dark / Light themes</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Dynamic app-wide switching via theme-aware palette + AtomikLookAndFeel; every screen/graph/dialog/heatmap chrome adapts live</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Theming &amp; Preferences</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Preferences / Settings tab</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Choose theme and unit system (SI / Imperial); displayed values convert, internal calcs stay SI</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Theming &amp; Preferences</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Persistent preferences</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Theme, units, grid visibility, measurement set, recent projects stored via PropertiesFile; broadcast via ChangeBroadcaster</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Project Workflow</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Project Dashboard at launch</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Separate window: new / open / recent projects; then opens main simulation window</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Project Workflow</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Project metadata capture</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Name, Engineer, Owner, Address, City, Country, Email, Mobile, Date - used in exports/reports</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Project Workflow</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Single-file .atmk projects</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Self-contained JSON: metadata + scene (speakers) + simulation settings; save/open</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Heatmap Export</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Client-ready heatmap sheet</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Header (logo, software name, title), project details, heatmap data (frequency, scale, units, legend) - generation logic untouched</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>PDF Report</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Multi-page PDF report</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Cover, Project Info, Input Parameters, Results, Graphs, Heatmaps (30/50/80/100 Hz), Summary - generated programmatically</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>PDF Report</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Custom PDF 1.4 writer (PdfDocument)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Vector text + embedded images, no external dependency</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>PDF Report</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>AcousticAnalysis module</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>RT60 (Sabine), absorption, transmission loss (mass-law), frequency response sampled from engine</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>PDF Report</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>GraphRender</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Line/bar charts rendered to images for the report</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Workspace / Grid / Layout</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Improved grid</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Major/minor lines, zoom-adaptive spacing (niceStep), higher contrast; show/hide toggle (persisted)</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Workspace / Grid / Layout</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Layout reference import</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Floor plans as background references - images (PNG/JPG) and DXF drawings</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Workspace / Grid / Layout</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>DXF parser (DxfImport)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Dependency-free 2D parser: LINE, LWPOLYLINE, POLYLINE/VERTEX, CIRCLE, ARC</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Workspace / Grid / Layout</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Layout alignment &amp; visibility tools</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Move, rotate, scale (width in m), opacity, show/hide, lock, snap-to-grid; live drag</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Array Presets</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Cardioid presets (2/3/4 sub)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Ready-to-use cardioid subwoofer arrays</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Array Presets</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>End-fired presets (2/3/4 sub)</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Auto-calculated spacing, delay, polarity, orientation; manually editable after placement</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Measurement Datasets</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Two selectable sets (kept separate)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Ground Plane = factory open-field (30/60/100/150/200 Hz, 1 m); Room = GYLT (30/80/200/500 Hz, 0.5/1 m)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Measurement Datasets</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Per-set heatmaps &amp; polar plots</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Switching reloads only that dataset + rebuilds directivity; each polar normalised to its own on-axis level; selection persisted</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Measurement Datasets</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Dynamic availability/legend</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Measured-polar 'available frequencies' and legend generated from the loaded dataset</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Responsive UI</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Minimum window size</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Main 1120x686, dashboard 680x537 - layout can never collapse/hide controls</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Responsive UI</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Fixed widescreen aspect ratio</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>1340:820 preserved during resize - no stretching distortion</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Responsive UI</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Defensive layout clamps</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Workspace visible (P1), side panels usable (P2), controls keep usable size (P3)</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Responsive UI</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Scrollable control panel</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Dense controls scroll (viewport) instead of shrinking</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Responsive UI</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Responsive header + 'more options' menu</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Title auto-shrinks/never clips; Export PDF / Save / Preferences fold into kebab menu at all sizes</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Branding &amp; Installer</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Atomik app icon embedded</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Windows .rc icon for exe, installer wizard, Add/Remove Programs, shortcuts; generated by make_icon.py</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Branding &amp; Installer</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Windows installer (Inno Setup)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Single Setup.exe: app + both datasets + fonts + icon; static CRT (no VC++ redist); per-user; uninstaller</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Versioning</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>1.0.0 -&gt; 1.1.0</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>App title shows v1.1; installer 1.1</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Color system</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Removed all red; cyan accent system</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Header red-&gt;near-white; accents red-&gt;grey-&gt;cyan; hierarchy headings #F5F7FA / labels #B8C0CC / muted #7E8794; bg #0D0D12 / panel #17171D; accent #44D9E6; success #53D769; warning #FF6B6B; PDF FR line red-&gt;steel-blue</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Measured directivity</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Data-driven normalisation</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Each curve normalised to its own on-axis level instead of hard-coded reference SPLs</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Measurement Datasets</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Option renames</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Open Field -&gt; Ground Plane; GYLT -&gt; Room (datasets unchanged)</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Buttons no longer overlap title</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Fixed overlap in narrow/short windows</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Title no longer clips</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Was showing 'v1.' instead of 'v1.1'</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Recent Projects</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Recent Projects hygiene</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Entries whose .atmk no longer exists are hidden and pruned automatically</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Installer</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Fresh install guarantee</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Per-user settings folder cleared on install + uninstall; no stale recent projects/settings on reinstall</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E39"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -174,10 +174,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1810,7 +1810,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1837,7 +1837,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1864,7 +1864,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2327,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2492,19 +2492,19 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Pan did nothing</t>
+          <t>Grid lines lighter over the field</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
+          <t>The light theme's opaque plotGrid overpowered the near-black field: major lines 100% -&gt; 42% alpha, minor 45% -&gt; 16%. Weights and thicknesses collected in UiConfig::PlotGrid</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2519,19 +2519,19 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Zoom anchored on the field corner</t>
+          <t>Pan did nothing</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -2543,25 +2543,52 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Zoom anchored on the field corner</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.1</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2774,7 +2801,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2801,7 +2828,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2990,7 +3017,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3017,7 +3044,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3044,7 +3071,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3071,7 +3098,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3098,7 +3125,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3125,7 +3152,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3152,7 +3179,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3179,7 +3206,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3206,7 +3233,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3233,7 +3260,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3488,7 +3515,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3608,7 +3635,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3635,7 +3662,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3662,7 +3689,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3689,7 +3716,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3944,7 +3971,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3971,7 +3998,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4955,7 +4982,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4982,7 +5009,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5009,7 +5036,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5036,7 +5063,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -174,10 +174,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1783,7 +1783,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1810,7 +1810,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1837,7 +1837,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1864,7 +1864,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2327,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2489,106 +2489,349 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Grid lines lighter over the field</t>
+          <t>Q21S units capped at 8</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>The light theme's opaque plotGrid overpowered the near-black field: major lines 100% -&gt; 42% alpha, minor 45% -&gt; 16%. Weights and thicknesses collected in UiConfig::PlotGrid</t>
+          <t>Enforced in ControlPanel::addSpeakerAt, which + Add, click-to-place and the terminal SPK all funnel through; each path reports the limit</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Pan did nothing</t>
+          <t>SPL solve runs on all cores</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
+          <t>0.4s -&gt; 0.1s for 8 units at 400 Hz / res 400. Rows split across workers; the four running maxima merge at the end and the per-cell scratch is per-worker (it was shared - a data race)</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+          <t>Ribbon</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Zoom anchored on the field corner</t>
+          <t>Opacity percentage never changed</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+          <t>MainComponent assigned over fillAlpha_.onValueChange, discarding the bar's readout sync. The bar owns the callback now and exposes onFillAlphaChanged</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Ribbon</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Opacity larger, slot widened, greyed when unusable</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Caption and value sized from measured glyphs in a 60-unit wider slot; disabled unless a filled shape is selected or a filling tool is armed</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Slow enough to look broken</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>15 s tick vs a 30 s throttle meant up to 45 s unsaved; now a 2 s tick with a 2 s floor</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Edits never showed as unsaved</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>applyResult reported a blanket Ready after every recompute, overwriting the dirty state set milliseconds earlier</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Fresh project claimed unsaved changes</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Construction runs the same change hooks an edit does; the flag is cleared once at the end of construction</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Grey control outlines, larger field labels</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>controlBorder #0C0C0C -&gt; #AFAFAF; sidebarFieldLabel 14.3 -&gt; 15.1; Measurement set hidden (one choice ships)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Recent Projects bigger</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Full button-row width, taller, larger text in both the control and its list (own LookAndFeel - the two read different hooks)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Grid lines lighter over the field</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>The light theme's opaque plotGrid overpowered the near-black field: major lines 100% -&gt; 42% alpha, minor 45% -&gt; 16%. Weights and thicknesses collected in UiConfig::PlotGrid</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Pan did nothing</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Zoom anchored on the field corner</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.1</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2801,7 +3044,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2828,7 +3071,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3017,7 +3260,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3044,7 +3287,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3071,7 +3314,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3098,7 +3341,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3125,7 +3368,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3152,7 +3395,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3179,7 +3422,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3206,7 +3449,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3233,7 +3476,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3260,7 +3503,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3515,7 +3758,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3635,7 +3878,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3662,7 +3905,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3689,7 +3932,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3716,7 +3959,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3971,7 +4214,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3998,7 +4241,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4982,7 +5225,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5009,7 +5252,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5036,7 +5279,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5063,7 +5306,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,22 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -171,13 +172,13 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -548,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -608,29 +609,29 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -640,224 +641,246 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -869,6 +892,208 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.2.x  -  Beta UI redesign (through betav1.2.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>~2026-07  |  Graph colors.pdf chrome between v1.1.0 and v1.3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Graph colors.pdf tokens</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Charcoal / white / ash / signal red + heatmap cool/hot stops in BrandTheme.h</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Signal Red accents</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Interactive accent #ED2227 for controls (later refined in 1.3.0 ATOMIK branding)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Heatmap</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Colour map + Rel. SPL chrome</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cool/hot stops and legend chrome aligned to brand mockups</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Light / dark chrome</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Sidebar density, speaker markers, plot chrome, header actions</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>betav1.2.3-style Release</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Signed Windows packaging of the redesign build (see Tools/make_ui_changelog_doc.py)</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1702,7 +1927,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1756,7 +1981,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1783,7 +2008,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1810,7 +2035,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1837,7 +2062,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1864,7 +2089,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1909,7 +2134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2103,7 +2328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2327,7 +2552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2340,14 +2565,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>v1.4.0.1  -  Detailed Changes</t>
+          <t>v1.4.0.2  -  Detailed Changes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18  |  No letterboxing + pan + true Q21S size</t>
+          <t>2026-09-19  |  8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2606,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -2391,24 +2616,24 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Middle-drag pans from any tool</t>
+          <t>Q21S units capped at 8</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No need to leave the tool you are drawing with</t>
+          <t>Enforced in ControlPanel::addSpeakerAt, which + Add, click-to-place and the terminal SPK all funnel through; each path reports the limit</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2418,51 +2643,51 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Never letterboxes</t>
+          <t>SPL solve runs on all cores</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>The fill-the-canvas fit is the zoom floor, so no pale margins at any zoom. Field stays 100 x 100 m with square cells; the cropped band is reached by panning</t>
+          <t>0.4s -&gt; 0.1s for 8 units at 400 Hz / res 400. Rows split across workers; the four running maxima merge at the end and the per-cell scratch is per-worker (it was shared - a data race)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Speakers</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Changed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Q21S dimensions corrected</t>
+          <t>Opacity percentage never changed</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m and the 1/r floor follows the true depth</t>
+          <t>MainComponent assigned over fillAlpha_.onValueChange, discarding the bar's readout sync. The bar owns the callback now and exposes onFillAlphaChanged</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Plot</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2472,39 +2697,39 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>SPL caption back at the canvas edge</t>
+          <t>Opacity larger, slot widened, greyed when unusable</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Was inset to the field's left edge, left over from a letterboxed view</t>
+          <t>Caption and value sized from measured glyphs in a 60-unit wider slot; disabled unless a filled shape is selected or a filling tool is armed</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Speakers</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8</t>
+          <t>Slow enough to look broken</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Enforced in ControlPanel::addSpeakerAt, which + Add, click-to-place and the terminal SPK all funnel through; each path reports the limit</t>
+          <t>15 s tick vs a 30 s throttle meant up to 45 s unsaved; now a 2 s tick with a 2 s floor</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2516,22 +2741,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>SPL solve runs on all cores</t>
+          <t>Edits never showed as unsaved</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>0.4s -&gt; 0.1s for 8 units at 400 Hz / res 400. Rows split across workers; the four running maxima merge at the end and the per-cell scratch is per-worker (it was shared - a data race)</t>
+          <t>applyResult reported a blanket Ready after every recompute, overwriting the dirty state set milliseconds earlier</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -2543,22 +2768,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ribbon</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
+          <t>Autosave</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Opacity percentage never changed</t>
+          <t>Fresh project claimed unsaved changes</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>MainComponent assigned over fillAlpha_.onValueChange, discarding the bar's readout sync. The bar owns the callback now and exposes onFillAlphaChanged</t>
+          <t>Construction runs the same change hooks an edit does; the flag is cleared once at the end of construction</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2570,7 +2795,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -2580,12 +2805,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Opacity larger, slot widened, greyed when unusable</t>
+          <t>Grey control outlines, larger field labels</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Caption and value sized from measured glyphs in a 60-unit wider slot; disabled unless a filled shape is selected or a filling tool is armed</t>
+          <t>controlBorder #0C0C0C -&gt; #AFAFAF; sidebarFieldLabel 14.3 -&gt; 15.1; Measurement set hidden (one choice ships)</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -2597,76 +2822,76 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Autosave</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Slow enough to look broken</t>
+          <t>Section titles sentence case</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>15 s tick vs a 30 s throttle meant up to 45 s unsaved; now a 2 s tick with a 2 s floor</t>
+          <t>1. Frequency (Hz) / 3. Selected Q21S / 4. Simulation; Q21S keeps its capitals as the product name</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Autosave</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Edits never showed as unsaved</t>
+          <t>Rel. SPL tick labels larger</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>applyResult reported a blanket Ready after every recompute, overwriting the dirty state set milliseconds earlier</t>
+          <t>legendTickOnScreen 11.0 -&gt; 14.0; the dB labels were too small to read</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Autosave</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Fresh project claimed unsaved changes</t>
+          <t>Recent Projects bigger</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Construction runs the same change hooks an edit does; the flag is cleared once at the end of construction</t>
+          <t>Full button-row width, taller, larger text in both the control and its list (own LookAndFeel - the two read different hooks)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -2678,7 +2903,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -2688,152 +2913,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Grey control outlines, larger field labels</t>
+          <t>Version -&gt; v1.4.0.2</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>controlBorder #0C0C0C -&gt; #AFAFAF; sidebarFieldLabel 14.3 -&gt; 15.1; Measurement set hidden (one choice ships)</t>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
           <t>2026-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Recent Projects bigger</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Full button-row width, taller, larger text in both the control and its list (own LookAndFeel - the two read different hooks)</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Grid lines lighter over the field</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>The light theme's opaque plotGrid overpowered the near-black field: major lines 100% -&gt; 42% alpha, minor 45% -&gt; 16%. Weights and thicknesses collected in UiConfig::PlotGrid</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Pan did nothing</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Zoom anchored on the field corner</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Zooming in walked off into empty space; it now holds the view centre</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Version -&gt; v1.4.0.1</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -2847,6 +2937,288 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.1  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18  |  No letterboxing + pan + true Q21S size</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Middle-drag pans from any tool</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>No need to leave the tool you are drawing with</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Never letterboxes</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>The fill-the-canvas fit is the zoom floor, so no pale margins at any zoom. Field stays 100 x 100 m with square cells; the cropped band is reached by panning</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Q21S dimensions corrected</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in) replaces an incorrect 750 x 784 x 917 mm set; footprint drawn at the field's px/m and the 1/r floor follows the true depth</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SPL caption back at the canvas edge</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Was inset to the field's left edge, left over from a letterboxed view</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Grid lines lighter over the field</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>The light theme's opaque plotGrid overpowered the near-black field: major lines 100% -&gt; 42% alpha, minor 45% -&gt; 16%. Weights and thicknesses collected in UiConfig::PlotGrid</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Pan did nothing</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>The view offset was clamped back to zero on every drag. Panning now moves the view across the field with no re-solve, so it is instant and placement is exact</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Zoom anchored on the field corner</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Zooming in walked off into empty space; it now holds the view centre</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.1</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3017,7 +3389,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3044,7 +3416,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3071,7 +3443,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3125,7 +3497,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3179,7 +3551,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3233,7 +3605,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3260,7 +3632,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3287,7 +3659,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3314,7 +3686,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3341,7 +3713,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3368,7 +3740,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3395,7 +3767,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3422,7 +3794,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3449,7 +3821,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3476,7 +3848,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3503,7 +3875,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3560,7 +3932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3758,7 +4130,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3785,7 +4157,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3815,7 +4187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3878,7 +4250,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3905,7 +4277,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3932,7 +4304,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3959,7 +4331,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4040,7 +4412,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4094,7 +4466,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4151,7 +4523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4214,7 +4586,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4241,7 +4613,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4325,7 +4697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4550,7 +4922,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4580,7 +4952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4982,7 +5354,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5036,7 +5408,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5090,7 +5462,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5144,7 +5516,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5198,7 +5570,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5225,7 +5597,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5252,7 +5624,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5279,7 +5651,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5306,7 +5678,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5349,206 +5721,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.2.x  -  Beta UI redesign (through betav1.2.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>~2026-07  |  Graph colors.pdf chrome between v1.1.0 and v1.3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Graph colors.pdf tokens</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Charcoal / white / ash / signal red + heatmap cool/hot stops in BrandTheme.h</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>~2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Signal Red accents</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Interactive accent #ED2227 for controls (later refined in 1.3.0 ATOMIK branding)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>~2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Heatmap</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Colour map + Rel. SPL chrome</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Cool/hot stops and legend chrome aligned to brand mockups</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>~2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Light / dark chrome</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Sidebar density, speaker markers, plot chrome, header actions</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>~2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>betav1.2.3-style Release</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Signed Windows packaging of the redesign build (see Tools/make_ui_changelog_doc.py)</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>~2026-07</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E9"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,23 +8,24 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,13 +73,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0053D769"/>
+      <color rgb="0044D9E6"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0044D9E6"/>
+      <color rgb="0053D769"/>
       <sz val="10"/>
     </font>
     <font>
@@ -169,7 +170,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,10 +182,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -549,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -609,51 +610,51 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.2</t>
+          <t>1.4.0.4</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>8-unit cap + parallel solve + autosave fixes</t>
+          <t>New Rel. SPL gradient + readable legend</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
+          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -663,224 +664,246 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -892,6 +915,777 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.3.0  -  Detailed Changes</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Development window 2026-08-12 -&gt; 2026-08-21 (portable ZIP same day)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Q21S BEM polar × 1/r SPL</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Far-field (~2 m) D(θ) coherent complex sum; r_spread floored at cabinet half-depth; absolute dB SPL from on-axis BEM; no ±5 m field stamp</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Array presets</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>MATLAB-style cardioid</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Rear 180°, polarity −1, −6 dB, 3.5 ms, ~0.01 m spacing; coherent engine sum</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Docs / pack</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Single-sub heatmap pack</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>docs/SINGLE_SUB_HEATMAP.md, native-Hz figures, generator script, dist_packages zip</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Version archive (HTML + MongoDB)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>version-archive/: releases from v1.3.0; source zip / macOS DMG / Windows ZIP (EXE+Data); local artifacts serve without Mongo</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Windows portable ZIP</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>EXE + MeasurementIntegrationPack\Data (Q21S CSVs); required for other PCs — bare EXE alone cannot load heatmaps</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Heatmap drawing tools</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Select, Pan, Pencil, Eraser, Ruler, Line + colour swatch; annotations in world metres</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Shapes + fill opacity</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Rectangle, Square, Circle tools with opacity slider; undo/redo covers shapes</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>BEM / directivity field math</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Tightened BEM and measured-directivity field formation (commit 633fc36)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Editing</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Undo / redo</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z, Ctrl+Y, Ctrl+Shift+Z; letter is lowercased so Caps Lock still works; drawings, cabinets, layouts, control-panel edits</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Windows Release exe</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Builds\Release\Atomik Simulation Engine.exe; installer/README at v1.3.0</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>DSP / UI (PS batch)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>IEC 1/3-octave frequencies</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>20, 25, 31, 40, 50, 63, 80, 100, 125, 160, 200, 250, 315, 400, 500 Hz</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Q21S footprint 750×784×917 mm</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Plan drawing + hit-test use true W×D; 1/r singularity floor = depth/2</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Heatmap uses 2 m BEM arc</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Array/SPL prediction keeps far-field arc; Measured Polar can still show nearer distances</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>World 100×100 m</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Was 30×30 m in v1.0; full-grid Q21S coverage prediction</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Q21S product set / native BEM Hz</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Catalogue 20,29,52,81,98,153,198,256,309,352,400,401 Hz; UI Ground Plane only</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Branding</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Product name</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Atomik Acoustic Simulation Engine -&gt; Atomik Simulation Engine; UI/PDF/CSV/installer/file version = v1.3.0</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Branding</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ATOMIK-only wordmark</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>AUDIO line removed; Atomik_Logo_Dark.png / Atomik_Logo_Light.png</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Statistics button</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Stats pill renamed Statistics; width sized to the full label</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Ground Plane only</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Measurement UI is Ground Plane (no Room set in live UI)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>DSP</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Legend / dB floor -6 dB steps</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Colourbar ticks and floor slider on -6 dB; dBfloor is display range only</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>XN18-n labels + Set to Default</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet labels use hyphen; Reset renamed Set to Default</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>No ±5 m BEM stamp on live map</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Full 100×100 m map follows polar × inverse-square instead of a near-field island</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Q21S pack path (vs legacy D:\shayam gui)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Prefer exe/repo MeasurementIntegrationPack with Q21S_52Hz_2p0m.csv marker; avoid Factory/ShyamGuild-only legacy pack</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Version no longer clips</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Was showing v1... instead of v1.3.0; layout uses real logo width</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Small-screen logo</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Header/dashboard wordmark -20%; Scale minFactor 0.78</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E29"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -954,7 +1748,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1008,7 +1802,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1062,7 +1856,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1093,7 +1887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1171,7 +1965,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1225,7 +2019,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1279,7 +2073,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1333,7 +2127,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1387,7 +2181,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1441,7 +2235,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1495,7 +2289,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1549,7 +2343,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1603,7 +2397,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1657,7 +2451,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1711,7 +2505,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1765,7 +2559,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1819,7 +2613,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1873,7 +2667,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1927,7 +2721,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1981,7 +2775,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2008,7 +2802,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2035,7 +2829,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2062,7 +2856,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2089,7 +2883,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2134,7 +2928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2328,7 +3122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2547,6 +3341,153 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.4  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21  |  New Rel. SPL gradient + readable legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>New Rel. SPL gradient</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515, replacing the seven-stop ramp. Stops are deliberately uneven (red to 30%, crossover at 47%), which is what lengthens the hot band</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Tick labels 18% larger</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>legendTickOnScreen 14.0 -&gt; 16.5</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.4</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2609,7 +3550,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2663,7 +3604,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2717,7 +3658,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2744,7 +3685,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2771,7 +3712,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2825,7 +3766,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2879,7 +3820,7 @@
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2936,7 +3877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2999,7 +3940,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3053,7 +3994,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3107,7 +4048,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3134,7 +4075,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3161,7 +4102,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3218,7 +4159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3281,7 +4222,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3335,7 +4276,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3389,7 +4330,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3416,7 +4357,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3443,7 +4384,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3497,7 +4438,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3551,7 +4492,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3605,7 +4546,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3632,7 +4573,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3659,7 +4600,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3686,7 +4627,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3713,7 +4654,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3740,7 +4681,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3767,7 +4708,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3794,7 +4735,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3821,7 +4762,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3848,7 +4789,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3875,7 +4816,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3932,7 +4873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3995,7 +4936,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4049,7 +4990,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4103,7 +5044,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4130,7 +5071,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4157,7 +5098,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4187,7 +5128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4250,7 +5191,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4277,7 +5218,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4304,7 +5245,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4331,7 +5272,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4358,7 +5299,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4412,7 +5353,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4466,7 +5407,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4523,7 +5464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4586,7 +5527,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4613,7 +5554,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4640,7 +5581,7 @@
           <t>Docs</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4697,7 +5638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4760,7 +5701,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4814,7 +5755,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4868,7 +5809,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4922,7 +5863,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4950,775 +5891,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.3.0  -  Detailed Changes</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Development window 2026-08-12 -&gt; 2026-08-21 (portable ZIP same day)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Q21S BEM polar × 1/r SPL</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Far-field (~2 m) D(θ) coherent complex sum; r_spread floored at cabinet half-depth; absolute dB SPL from on-axis BEM; no ±5 m field stamp</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Array presets</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>MATLAB-style cardioid</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Rear 180°, polarity −1, −6 dB, 3.5 ms, ~0.01 m spacing; coherent engine sum</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Docs / pack</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Single-sub heatmap pack</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>docs/SINGLE_SUB_HEATMAP.md, native-Hz figures, generator script, dist_packages zip</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Version archive (HTML + MongoDB)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>version-archive/: releases from v1.3.0; source zip / macOS DMG / Windows ZIP (EXE+Data); local artifacts serve without Mongo</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Windows portable ZIP</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>EXE + MeasurementIntegrationPack\Data (Q21S CSVs); required for other PCs — bare EXE alone cannot load heatmaps</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Heatmap drawing tools</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Select, Pan, Pencil, Eraser, Ruler, Line + colour swatch; annotations in world metres</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Shapes + fill opacity</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Rectangle, Square, Circle tools with opacity slider; undo/redo covers shapes</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>BEM / directivity field math</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Tightened BEM and measured-directivity field formation (commit 633fc36)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Editing</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Undo / redo</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+Z, Ctrl+Y, Ctrl+Shift+Z; letter is lowercased so Caps Lock still works; drawings, cabinets, layouts, control-panel edits</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Windows Release exe</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Builds\Release\Atomik Simulation Engine.exe; installer/README at v1.3.0</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>DSP / UI (PS batch)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>IEC 1/3-octave frequencies</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>20, 25, 31, 40, 50, 63, 80, 100, 125, 160, 200, 250, 315, 400, 500 Hz</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Cabinet</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Q21S footprint 750×784×917 mm</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Plan drawing + hit-test use true W×D; 1/r singularity floor = depth/2</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Heatmap uses 2 m BEM arc</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Array/SPL prediction keeps far-field arc; Measured Polar can still show nearer distances</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>World 100×100 m</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Was 30×30 m in v1.0; full-grid Q21S coverage prediction</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Measurement</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Q21S product set / native BEM Hz</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue 20,29,52,81,98,153,198,256,309,352,400,401 Hz; UI Ground Plane only</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Branding</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Product name</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Atomik Acoustic Simulation Engine -&gt; Atomik Simulation Engine; UI/PDF/CSV/installer/file version = v1.3.0</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Branding</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ATOMIK-only wordmark</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>AUDIO line removed; Atomik_Logo_Dark.png / Atomik_Logo_Light.png</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Statistics button</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Stats pill renamed Statistics; width sized to the full label</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Measurement</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Ground Plane only</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Measurement UI is Ground Plane (no Room set in live UI)</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>DSP</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Legend / dB floor -6 dB steps</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Colourbar ticks and floor slider on -6 dB; dBfloor is display range only</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>XN18-n labels + Set to Default</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Cabinet labels use hyphen; Reset renamed Set to Default</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>No ±5 m BEM stamp on live map</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Full 100×100 m map follows polar × inverse-square instead of a near-field island</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Q21S pack path (vs legacy D:\shayam gui)</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Prefer exe/repo MeasurementIntegrationPack with Q21S_52Hz_2p0m.csv marker; avoid Factory/ShyamGuild-only legacy pack</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Version no longer clips</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Was showing v1... instead of v1.3.0; layout uses real logo width</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Small-screen logo</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Header/dashboard wordmark -20%; Scale minFactor 0.78</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E29"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,24 +8,25 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.5 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -73,13 +74,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0044D9E6"/>
+      <color rgb="0053D769"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0053D769"/>
+      <color rgb="0044D9E6"/>
       <sz val="10"/>
     </font>
     <font>
@@ -176,13 +177,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -550,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,73 +611,73 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.4</t>
+          <t>1.4.0.5</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>New Rel. SPL gradient + readable legend</t>
+          <t>BEM 2inch as a second speaker model</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
+          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.2</t>
+          <t>1.4.0.4</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>8-unit cap + parallel solve + autosave fixes</t>
+          <t>New Rel. SPL gradient + readable legend</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
+          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -686,224 +687,246 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -915,6 +938,261 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.3.5  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26  |  Mic tool + embedded Q21S Windows Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Mic tool</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Virtual receivers on heatmap</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Add Mic / Place on ring; ring snap 1/2/4/8 m; live relative dB; Esc cancels arm</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Mic tool</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Show Degrees toggle</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Angle vs Q21S facing (0° = front, CCW) shown before dB on mic labels</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mic tool</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Floating Frequency Response window</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Opens when mics exist; does not shrink the plot; curves from sampleIntensityAt</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Mic tool</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Tak snap sound</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>In-memory WAV via winmm; no .wav asset on disk</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Embedded Q21S CSVs in EXE</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>EmbeddedQ21SData; heatmaps work without MeasurementIntegrationPack or Excel</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Windows Setup v1.3.5</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>AtomikSimulationEngine-Setup-v1.3.5.exe — EXE + fonts only (no Excel)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Installer drops Excel folders</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>setup.iss no longer ships Factory Readings / shyamGuildMeasurements xlsx</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -992,7 +1270,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1019,7 +1297,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1046,7 +1324,7 @@
           <t>Docs / pack</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1073,7 +1351,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1100,7 +1378,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1127,7 +1405,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1154,7 +1432,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1181,7 +1459,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1208,7 +1486,7 @@
           <t>Editing</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1235,7 +1513,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1262,7 +1540,7 @@
           <t>DSP / UI (PS batch)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1289,7 +1567,7 @@
           <t>Cabinet</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1316,7 +1594,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1343,7 +1621,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1370,7 +1648,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1397,7 +1675,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1424,7 +1702,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1451,7 +1729,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1478,7 +1756,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1505,7 +1783,7 @@
           <t>DSP</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1532,7 +1810,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1559,7 +1837,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1586,7 +1864,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1613,7 +1891,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1640,7 +1918,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1685,7 +1963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1748,7 +2026,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1775,7 +2053,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1802,7 +2080,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1829,7 +2107,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1856,7 +2134,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1887,7 +2165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1965,7 +2243,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1992,7 +2270,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2019,7 +2297,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2046,7 +2324,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2073,7 +2351,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2100,7 +2378,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2127,7 +2405,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2154,7 +2432,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2181,7 +2459,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2208,7 +2486,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2235,7 +2513,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2262,7 +2540,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2289,7 +2567,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2316,7 +2594,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2343,7 +2621,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2370,7 +2648,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2397,7 +2675,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2424,7 +2702,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2451,7 +2729,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2478,7 +2756,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2505,7 +2783,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2532,7 +2810,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2559,7 +2837,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2586,7 +2864,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2613,7 +2891,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2640,7 +2918,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2667,7 +2945,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2694,7 +2972,7 @@
           <t>Versioning</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2721,7 +2999,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2748,7 +3026,7 @@
           <t>Measured directivity</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2775,7 +3053,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2802,7 +3080,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2829,7 +3107,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2856,7 +3134,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2883,7 +3161,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2928,7 +3206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3122,7 +3400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3341,6 +3619,261 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.5  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25  |  BEM 2inch as a second speaker model</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>BEM 2inch as a second speaker model</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Speaker model picker in sidebar section 2 chooses what new units are created as; every unit carries its own model tag, so a scene can mix Q21S and BEM 2inch and each is simulated from its own measured data - never blended</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Own frequency catalogue</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>9 native BEM bands 64, 135, 243, 507, 1057, 1904, 3971, 8280, 17266 Hz; Q21S keeps its own 20 - 401 Hz list. Switching models rebuilds the Frequency dropdown from scratch and each model remembers its last band</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Own embedded measured pack</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>BEM2inch_&lt;Hz&gt;Hz_&lt;dist&gt;m.csv polars at 0.5/1.0/2.0 m plus BEM2inch_Field_&lt;Hz&gt;Hz.q21f absolute fields, baked in as EmbeddedBEM2inchData so the EXE still runs with no sidecar Data/ folder</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-inch BEM exporter</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>docs/bem2inch_plots/export_2inch_native_hz_pack.py. Handles this set's 6-column layout and its half-plane domain (z = 0..+10 m, source at the edge): the rear hemisphere is synthesised by tapering from the measured grazing level to min(grazing, on-axis - 25 dB) instead of extrapolating</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Unit names use a model tag, numbered per model</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>A BEM unit placed second overall but first of its model reads BEM2inch_1, not BEM 2inch_2. Applied to plot label, sidebar list, properties dialog, Info panel, mic reference picker and PDF report so one unit reads the same everywhere; headings keep the spaced display name</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Measurement set row removed</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Redundant with the Speaker model picker, which is now the single control for which device is in use</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.5</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3403,7 +3936,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3430,7 +3963,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3457,7 +3990,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3487,7 +4020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3550,7 +4083,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3577,7 +4110,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3604,7 +4137,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3631,7 +4164,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3658,7 +4191,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3685,7 +4218,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3712,7 +4245,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3739,7 +4272,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3766,7 +4299,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3793,7 +4326,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3820,7 +4353,7 @@
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3847,7 +4380,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3877,7 +4410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3940,7 +4473,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3967,7 +4500,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3994,7 +4527,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4021,7 +4554,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4048,7 +4581,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4075,7 +4608,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4102,7 +4635,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4129,7 +4662,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4159,7 +4692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4222,7 +4755,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4249,7 +4782,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4276,7 +4809,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4303,7 +4836,7 @@
           <t>Naming</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4330,7 +4863,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4357,7 +4890,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4384,7 +4917,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4411,7 +4944,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4438,7 +4971,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4465,7 +4998,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4492,7 +5025,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4519,7 +5052,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4546,7 +5079,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4573,7 +5106,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4600,7 +5133,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4627,7 +5160,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4654,7 +5187,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4681,7 +5214,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4708,7 +5241,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4735,7 +5268,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4762,7 +5295,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4789,7 +5322,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4816,7 +5349,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4843,7 +5376,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4873,7 +5406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4936,7 +5469,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4963,7 +5496,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4990,7 +5523,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5017,7 +5550,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5044,7 +5577,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5071,7 +5604,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5098,7 +5631,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5128,7 +5661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5191,7 +5724,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5218,7 +5751,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5245,7 +5778,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5272,7 +5805,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5299,7 +5832,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5326,7 +5859,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5353,7 +5886,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5380,7 +5913,7 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5407,7 +5940,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5434,7 +5967,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5464,7 +5997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5527,7 +6060,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5554,7 +6087,7 @@
           <t>Plot Snap</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5581,7 +6114,7 @@
           <t>Docs</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5608,7 +6141,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5626,261 +6159,6 @@
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.3.5  -  Detailed Changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26  |  Mic tool + embedded Q21S Windows Setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Mic tool</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Virtual receivers on heatmap</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Add Mic / Place on ring; ring snap 1/2/4/8 m; live relative dB; Esc cancels arm</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Mic tool</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Show Degrees toggle</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Angle vs Q21S facing (0° = front, CCW) shown before dB on mic labels</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Mic tool</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Floating Frequency Response window</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Opens when mics exist; does not shrink the plot; curves from sampleIntensityAt</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Mic tool</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Tak snap sound</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>In-memory WAV via winmm; no .wav asset on disk</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Embedded Q21S CSVs in EXE</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>EmbeddedQ21SData; heatmaps work without MeasurementIntegrationPack or Excel</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Windows Setup v1.3.5</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>AtomikSimulationEngine-Setup-v1.3.5.exe — EXE + fonts only (no Excel)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Installer drops Excel folders</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>setup.iss no longer ships Factory Readings / shyamGuildMeasurements xlsx</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,25 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.5 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.6 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.5 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,12 +75,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0053D769"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="0044D9E6"/>
       <sz val="10"/>
     </font>
@@ -87,6 +82,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF6B6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0053D769"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -551,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -611,95 +612,95 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.5</t>
+          <t>1.4.0.6</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>BEM 2inch as a second speaker model</t>
+          <t>Export metrics strip redesigned; Peak SPL withdrawn</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
+          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; /utf-8 added to both build configs, fixing the mojibake separators in exported text</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.4</t>
+          <t>1.4.0.5</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>New Rel. SPL gradient + readable legend</t>
+          <t>BEM 2inch as a second speaker model</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
+          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.2</t>
+          <t>1.4.0.4</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>8-unit cap + parallel solve + autosave fixes</t>
+          <t>New Rel. SPL gradient + readable legend</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
+          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -709,224 +710,246 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -938,6 +961,180 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.3.6  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31  |  Mic ring snap + shape-edge Snap tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Mic tool</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Original Drag::Mic ring snap</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Cursor-follow + 1/2/4/8 m latch + tak; no sticky lock from SelectionMove/object snap</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Plot Snap</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Tak when shapes meet</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Sound on rising edge of annotation edge contact; not speakers/mics/centres</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>start.md</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Repo-root build/run instructions for Windows Debug/Release and MSBuild</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Version → v1.3.6</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>App, resource, installer defines, archive HTML/json</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1000,7 +1197,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1027,7 +1224,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1054,7 +1251,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1081,7 +1278,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1108,7 +1305,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1135,7 +1332,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1162,7 +1359,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1192,7 +1389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1270,7 +1467,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1297,7 +1494,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1324,7 +1521,7 @@
           <t>Docs / pack</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1351,7 +1548,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1378,7 +1575,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1405,7 +1602,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1432,7 +1629,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1459,7 +1656,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1486,7 +1683,7 @@
           <t>Editing</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1513,7 +1710,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1540,7 +1737,7 @@
           <t>DSP / UI (PS batch)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1567,7 +1764,7 @@
           <t>Cabinet</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1594,7 +1791,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1621,7 +1818,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1648,7 +1845,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1675,7 +1872,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1702,7 +1899,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1729,7 +1926,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1756,7 +1953,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1783,7 +1980,7 @@
           <t>DSP</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1810,7 +2007,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1837,7 +2034,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1864,7 +2061,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1891,7 +2088,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1918,7 +2115,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1963,7 +2160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2026,7 +2223,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2053,7 +2250,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2080,7 +2277,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2107,7 +2304,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2134,7 +2331,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2165,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2243,7 +2440,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2270,7 +2467,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2297,7 +2494,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2324,7 +2521,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2351,7 +2548,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2378,7 +2575,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2405,7 +2602,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2432,7 +2629,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2459,7 +2656,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2486,7 +2683,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2513,7 +2710,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2540,7 +2737,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2567,7 +2764,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2594,7 +2791,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2621,7 +2818,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2648,7 +2845,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2675,7 +2872,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2702,7 +2899,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2729,7 +2926,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2756,7 +2953,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2783,7 +2980,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2810,7 +3007,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2837,7 +3034,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2864,7 +3061,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2891,7 +3088,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2918,7 +3115,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2945,7 +3142,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2972,7 +3169,7 @@
           <t>Versioning</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2999,7 +3196,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3026,7 +3223,7 @@
           <t>Measured directivity</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3053,7 +3250,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3080,7 +3277,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3107,7 +3304,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3134,7 +3331,7 @@
           <t>Recent Projects</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3161,7 +3358,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3206,7 +3403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3400,7 +3597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3637,14 +3834,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>v1.4.0.5  -  Detailed Changes</t>
+          <t>v1.4.0.6  -  Detailed Changes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25  |  BEM 2inch as a second speaker model</t>
+          <t>2026-09-26  |  Export metrics strip redesigned; Peak SPL withdrawn</t>
         </is>
       </c>
     </row>
@@ -3678,162 +3875,162 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Export (PNG)</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>BEM 2inch as a second speaker model</t>
+          <t>Metrics strip redesigned</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Speaker model picker in sidebar section 2 chooses what new units are created as; every unit carries its own model tag, so a scene can mix Q21S and BEM 2inch and each is simulated from its own measured data - never blended</t>
+          <t>Charcoal band and its duplicate wordmark replaced by a light labelled key/value panel matching the project block, with a red rule tying it to the header and a plain sign-off line beneath. All metrics kept and headed: Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Export (PNG)</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Changed</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Own frequency catalogue</t>
+          <t>Scale shown as relative range</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>9 native BEM bands 64, 135, 243, 507, 1057, 1904, 3971, 8280, 17266 Hz; Q21S keeps its own 20 - 401 Hz list. Switching models rebuilds the Frequency dropdown from scratch and each model remembers its last band</t>
+          <t>0 to -N dB, matching what the gradient legend displays, rather than an absolute span</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Own embedded measured pack</t>
+          <t>Peak SPL removed from PNG and PDF</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>BEM2inch_&lt;Hz&gt;Hz_&lt;dist&gt;m.csv polars at 0.5/1.0/2.0 m plus BEM2inch_Field_&lt;Hz&gt;Hz.q21f absolute fields, baked in as EmbeddedBEM2inchData so the EXE still runs with no sidecar Data/ folder</t>
+          <t>Withdrawn rather than shown wrong - see the calibration fix below</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Added</t>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2-inch BEM exporter</t>
+          <t>Absolute calibration declared, not inferred</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>docs/bem2inch_plots/export_2inch_native_hz_pack.py. Handles this set's 6-column layout and its half-plane domain (z = 0..+10 m, source at the edge): the rear hemisphere is synthesised by tapering from the measured grazing level to min(grazing, on-axis - 25 dB) instead of extrapolating</t>
+          <t>hasAbsolute was a bare magnitude test (on-axis &gt; 20 dB), which promoted the 2" horn's unit-drive BEM data to absolute because 36-46 dB clears it; the export then printed 43.5 dB SPL beside Q21S's 116.1 dB. Now declared per source in MeasurementData::calibrationFor()</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Changed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Unit names use a model tag, numbered per model</t>
+          <t>/utf-8 added to both configurations</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>A BEM unit placed second overall but first of its model reads BEM2inch_1, not BEM 2inch_2. Applied to plot label, sidebar list, properties dialog, Info panel, mic reference picker and PDF report so one unit reads the same everywhere; headings keep the spaced display name</t>
+          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Sidebar</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Measurement set row removed</t>
+          <t>Overview prose no longer describes peak as absolute</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Redundant with the Speaker model picker, which is now the single control for which device is in use</t>
+          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3843,14 +4040,14 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Version -&gt; v1.4.0.5</t>
+          <t>Version -&gt; v1.4.0.6</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -3860,7 +4057,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3874,6 +4071,261 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.5  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25  |  BEM 2inch as a second speaker model</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>BEM 2inch as a second speaker model</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Speaker model picker in sidebar section 2 chooses what new units are created as; every unit carries its own model tag, so a scene can mix Q21S and BEM 2inch and each is simulated from its own measured data - never blended</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Own frequency catalogue</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>9 native BEM bands 64, 135, 243, 507, 1057, 1904, 3971, 8280, 17266 Hz; Q21S keeps its own 20 - 401 Hz list. Switching models rebuilds the Frequency dropdown from scratch and each model remembers its last band</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Own embedded measured pack</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>BEM2inch_&lt;Hz&gt;Hz_&lt;dist&gt;m.csv polars at 0.5/1.0/2.0 m plus BEM2inch_Field_&lt;Hz&gt;Hz.q21f absolute fields, baked in as EmbeddedBEM2inchData so the EXE still runs with no sidecar Data/ folder</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-inch BEM exporter</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>docs/bem2inch_plots/export_2inch_native_hz_pack.py. Handles this set's 6-column layout and its half-plane domain (z = 0..+10 m, source at the edge): the rear hemisphere is synthesised by tapering from the measured grazing level to min(grazing, on-axis - 25 dB) instead of extrapolating</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Unit names use a model tag, numbered per model</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>A BEM unit placed second overall but first of its model reads BEM2inch_1, not BEM 2inch_2. Applied to plot label, sidebar list, properties dialog, Info panel, mic reference picker and PDF report so one unit reads the same everywhere; headings keep the spaced display name</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Measurement set row removed</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Redundant with the Speaker model picker, which is now the single control for which device is in use</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.5</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3936,7 +4388,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3963,7 +4415,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3990,7 +4442,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4020,7 +4472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4083,7 +4535,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4110,7 +4562,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4137,7 +4589,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4164,7 +4616,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4191,7 +4643,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4218,7 +4670,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4245,7 +4697,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4272,7 +4724,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4299,7 +4751,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4326,7 +4778,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4353,7 +4805,7 @@
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4380,7 +4832,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4410,7 +4862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4473,7 +4925,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4500,7 +4952,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4527,7 +4979,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4554,7 +5006,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4581,7 +5033,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4608,7 +5060,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4635,7 +5087,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4662,7 +5114,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4692,7 +5144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4755,7 +5207,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4782,7 +5234,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4809,7 +5261,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4836,7 +5288,7 @@
           <t>Naming</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4863,7 +5315,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4890,7 +5342,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4917,7 +5369,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4944,7 +5396,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4971,7 +5423,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4998,7 +5450,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5025,7 +5477,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5052,7 +5504,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5079,7 +5531,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5106,7 +5558,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5133,7 +5585,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5160,7 +5612,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5187,7 +5639,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5214,7 +5666,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5241,7 +5693,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5268,7 +5720,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5295,7 +5747,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5322,7 +5774,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5349,7 +5801,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5376,7 +5828,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5406,7 +5858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5469,7 +5921,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5496,7 +5948,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5523,7 +5975,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5550,7 +6002,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5577,7 +6029,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5604,7 +6056,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5631,7 +6083,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5661,7 +6113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5724,7 +6176,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5751,7 +6203,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5778,7 +6230,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5805,7 +6257,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5832,7 +6284,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5859,7 +6311,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5886,7 +6338,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5913,7 +6365,7 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5940,7 +6392,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5967,7 +6419,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5985,180 +6437,6 @@
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.3.6  -  Detailed Changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31  |  Mic ring snap + shape-edge Snap tak</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Mic tool</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Original Drag::Mic ring snap</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Cursor-follow + 1/2/4/8 m latch + tak; no sticky lock from SelectionMove/object snap</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Plot Snap</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Tak when shapes meet</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Sound on rising edge of annotation edge contact; not speakers/mics/centres</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>start.md</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Repo-root build/run instructions for Windows Debug/Release and MSBuild</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Version → v1.3.6</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>App, resource, installer defines, archive HTML/json</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; /utf-8 added to both build configs, fixing the mojibake separators in exported text</t>
+          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; exports now truly overwrite (PNG and CSV were being appended to an existing file, so the old content kept showing); /utf-8 added to both build configs, fixing the mojibake separators</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3983,7 +3983,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>/utf-8 added to both configurations</t>
+          <t>Saving over an existing file now replaces it</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
+          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4010,22 +4010,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Overview prose no longer describes peak as absolute</t>
+          <t>/utf-8 added to both configurations</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4037,25 +4037,52 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Overview prose no longer describes peak as absolute</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.6</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -3821,7 +3821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3983,7 +3983,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Saving over an existing file now replaces it</t>
+          <t>Selecting a model or unit no longer re-solves</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
+          <t>The model picker called notifyChanged() and getParams() read the sim frequency from the Frequency dropdown, so switching model moved the whole scene onto the other model's band and redrew SPL for untouched speakers. The scene now owns its frequency, seeded from the first unit placed and changed only by an explicit dropdown pick; selecting a unit repoints the Frequency list to that unit's model for reference only</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>/utf-8 added to both configurations</t>
+          <t>Saving over an existing file now replaces it</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
+          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Overview prose no longer describes peak as absolute</t>
+          <t>/utf-8 added to both configurations</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -4064,25 +4064,52 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Overview prose no longer describes peak as absolute</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.6</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -3821,7 +3821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3986,19 +3986,19 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Selecting a model or unit no longer re-solves</t>
+          <t>Per-model cabinet dimensions</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>The model picker called notifyChanged() and getParams() read the sim frequency from the Frequency dropdown, so switching model moved the whole scene onto the other model's band and redrew SPL for untouched speakers. The scene now owns its frequency, seeded from the first unit placed and changed only by an explicit dropdown pick; selecting a unit repoints the Frequency list to that unit's model for reference only</t>
+          <t>Cabinet size was one hardcoded Q21S set used for every model. Each model now carries its own enclosure via cabinetFor(): the 2" horn is 459 x 276.5 x 150 mm against the Q21S's 679 x 1546 x 1024 mm. Plan marker, Properties dialog, Info panel and the engine's per-speaker near-field floor all read from it</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Saving over an existing file now replaces it</t>
+          <t>Unit row no longer wraps</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
+          <t>The unit dropdown took whatever the two fixed-width buttons left, too narrow for a name like BEM2inch-1; the combo now gets a guaranteed share of the row</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>/utf-8 added to both configurations</t>
+          <t>Selecting a model or unit no longer re-solves</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
+          <t>The model picker called notifyChanged() and getParams() read the sim frequency from the Frequency dropdown, so switching model moved the whole scene onto the other model's band and redrew SPL for untouched speakers. The scene now owns its frequency, seeded from the first unit placed and changed only by an explicit dropdown pick; selecting a unit repoints the Frequency list to that unit's model for reference only</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -4064,22 +4064,22 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Overview prose no longer describes peak as absolute</t>
+          <t>Saving over an existing file now replaces it</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -4091,25 +4091,79 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>/utf-8 added to both configurations</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Overview prose no longer describes peak as absolute</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.6</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -181,10 +181,10 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1077,7 +1077,7 @@
           <t>Docs</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1197,7 +1197,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1224,7 +1224,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1251,7 +1251,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1278,7 +1278,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1305,7 +1305,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1332,7 +1332,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1467,7 +1467,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1494,7 +1494,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1521,7 +1521,7 @@
           <t>Docs / pack</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1548,7 +1548,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1575,7 +1575,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1602,7 +1602,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1629,7 +1629,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1656,7 +1656,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1683,7 +1683,7 @@
           <t>Editing</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1710,7 +1710,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1737,7 +1737,7 @@
           <t>DSP / UI (PS batch)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2331,7 +2331,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2440,7 +2440,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2467,7 +2467,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2494,7 +2494,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2521,7 +2521,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2548,7 +2548,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2575,7 +2575,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2602,7 +2602,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2629,7 +2629,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2656,7 +2656,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2683,7 +2683,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2710,7 +2710,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2737,7 +2737,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2764,7 +2764,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2791,7 +2791,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2818,7 +2818,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2845,7 +2845,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2872,7 +2872,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2899,7 +2899,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2926,7 +2926,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2953,7 +2953,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2980,7 +2980,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3007,7 +3007,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3034,7 +3034,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3061,7 +3061,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3088,7 +3088,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3115,7 +3115,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3142,7 +3142,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3821,7 +3821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3986,19 +3986,19 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Added</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Per-model cabinet dimensions</t>
+          <t>Q21S width and height were swapped</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Cabinet size was one hardcoded Q21S set used for every model. Each model now carries its own enclosure via cabinetFor(): the 2" horn is 459 x 276.5 x 150 mm against the Q21S's 679 x 1546 x 1024 mm. Plan marker, Properties dialog, Info panel and the engine's per-speaker near-field floor all read from it</t>
+          <t>Manufacturer quotes W x H x D = 1546 x 679 x 1024 mm (60.86 x 26.73 x 40.31 in); the code mapped them as H x W x D, so the cabinet was 679 mm wide and 1546 mm tall instead of the reverse and its plan footprint was drawn at under half its true width. Depth unchanged, so the near-field floor is unaffected</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4010,22 +4010,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Sidebar</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Unit row no longer wraps</t>
+          <t>Per-model cabinet dimensions</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>The unit dropdown took whatever the two fixed-width buttons left, too narrow for a name like BEM2inch-1; the combo now gets a guaranteed share of the row</t>
+          <t>Cabinet size was one hardcoded Q21S set used for every model. Each model now carries its own enclosure via cabinetFor(): the 2" horn is 459 x 276.5 x 150 mm against the Q21S's 1546 x 679 x 1024 mm. Plan marker, Properties dialog, Info panel and the engine's per-speaker near-field floor all read from it</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Speakers</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Selecting a model or unit no longer re-solves</t>
+          <t>Unit row no longer wraps</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>The model picker called notifyChanged() and getParams() read the sim frequency from the Frequency dropdown, so switching model moved the whole scene onto the other model's band and redrew SPL for untouched speakers. The scene now owns its frequency, seeded from the first unit placed and changed only by an explicit dropdown pick; selecting a unit repoints the Frequency list to that unit's model for reference only</t>
+          <t>The unit dropdown took whatever the two fixed-width buttons left, too narrow for a name like BEM2inch-1; the combo now gets a guaranteed share of the row</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -4064,7 +4064,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Saving over an existing file now replaces it</t>
+          <t>Selecting a model or unit no longer re-solves</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
+          <t>The model picker called notifyChanged() and getParams() read the sim frequency from the Frequency dropdown, so switching model moved the whole scene onto the other model's band and redrew SPL for untouched speakers. The scene now owns its frequency, seeded from the first unit placed and changed only by an explicit dropdown pick; selecting a unit repoints the Frequency list to that unit's model for reference only</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>/utf-8 added to both configurations</t>
+          <t>Saving over an existing file now replaces it</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
+          <t>FileOutputStream opens an existing file at its END, so the PNG sheet and SPL CSV were appended rather than replacing what was there; viewers decode the first image in the file, so the old one kept showing while the timestamp updated. All three writers rewind and truncate first</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -4118,22 +4118,22 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Overview prose no longer describes peak as absolute</t>
+          <t>/utf-8 added to both configurations</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+          <t>Sources are UTF-8 without a BOM, so MSVC read them as CP1252 and baked mojibake into the binary (the mis-rendered separators in exported text). Fixes all 19 non-ASCII literals</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -4145,25 +4145,52 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Overview prose no longer describes peak as absolute</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Section 3.1 now refers to levels relative to the Rel. SPL = 0 dB cell</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Version -&gt; v1.4.0.6</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>App, resource, installer, archive HTML/json, Windows Release EXE</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
@@ -4241,7 +4268,7 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4268,7 +4295,7 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4295,7 +4322,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4322,7 +4349,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4643,7 +4670,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5033,7 +5060,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5315,7 +5342,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5342,7 +5369,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5369,7 +5396,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6029,7 +6056,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6056,7 +6083,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6083,7 +6110,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6110,7 +6137,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6137,7 +6164,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6392,7 +6419,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6419,7 +6446,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -8,26 +8,27 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.6 Changes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.5 Changes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.7 Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.6 Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.5 Changes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.4 Changes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.2 Changes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0.1 Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.4.0 Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.8 Changes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.7 Changes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.6 Changes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.5 Changes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.3.0 Changes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.2.x Beta UI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.1.0 Changes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.0.0 Baseline" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'v1.3.0 Changes'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'v1.2.x Beta UI'!$A$4:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'v1.1.0 Changes'!$A$4:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,6 +76,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="0053D769"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="0044D9E6"/>
       <sz val="10"/>
     </font>
@@ -82,12 +89,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF6B6B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0053D769"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -178,10 +179,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -552,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -612,117 +613,117 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.6</t>
+          <t>1.4.0.7</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Export metrics strip redesigned; Peak SPL withdrawn</t>
+          <t>Rotation handle + sketch sizes + 3D cabinet view</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; exports now truly overwrite (PNG and CSV were being appended to an existing file, so the old content kept showing); /utf-8 added to both build configs, fixing the mojibake separators</t>
+          <t>5-degree rotation handle on selected units (rotationDeg saved, re-solves the field); plan footprints from the placement sketch (Q21S 900 x 1000 mm, BEM 2inch 500 x 500 mm); Show sizes dimensions each cabinet W / D / H on the plan; View in 3D from Properties with W / H / D on the box's edges; zero non-ASCII in UI string literals (mojibake fixed); elevation views, height / tilt and Z / F shortcuts built but hidden behind a flag</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.5</t>
+          <t>1.4.0.6</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>BEM 2inch as a second speaker model</t>
+          <t>Export metrics strip redesigned; Peak SPL withdrawn</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
+          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; exports now truly overwrite (PNG and CSV were being appended to an existing file, so the old content kept showing); /utf-8 added to both build configs, fixing the mojibake separators</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.4</t>
+          <t>1.4.0.5</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>New Rel. SPL gradient + readable legend</t>
+          <t>BEM 2inch as a second speaker model</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
+          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.2</t>
+          <t>1.4.0.4</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>8-unit cap + parallel solve + autosave fixes</t>
+          <t>New Rel. SPL gradient + readable legend</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
+          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -732,224 +733,246 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.6</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Mic snap + shape-edge tak</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>Mic tool + embedded Q21S Setup</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.x</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>~2026-07</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Beta UI redesign (betav1.2.3)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -961,6 +984,342 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.3.7  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02  |  Gain fix + text box + clean slate + drawing UX</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Gain (dB) affects SPL</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Unity-gain reference normalisation; per-speaker level and array balance visible on heatmap</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Delete all selected</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Sidebar Delete removes every speaker in plot multi-selection, not just primary unit</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Line first stroke</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Minimum drag distance prevents accidental micro-line consuming first click</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Esc + Shape menu</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Esc returns to Select from drawing tools; cursor tool no longer opens Shape menu</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Command terminal</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Bottom-panel terminal replaces Phase/Arrival/STI placeholders; cls/clear supported</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Plot tools</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Text box annotations</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Shape menu Text Box; fill colour like shapes; rotation handle; double-click edit</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Delay slider max 10 ms</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Was 50 ms; presets unchanged</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Clean slate on first open</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>No default speakers until user adds a Q21S unit</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Range off by default</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Distance rings hidden until Range toggle is on</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Version → v1.3.7 (refresh)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>App, resource, installer defines, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1023,7 +1382,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -1077,7 +1436,7 @@
           <t>Docs</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1104,7 +1463,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1134,7 +1493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1197,7 +1556,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1224,7 +1583,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1251,7 +1610,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1278,7 +1637,7 @@
           <t>Mic tool</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1305,7 +1664,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1332,7 +1691,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1359,7 +1718,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1389,7 +1748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1467,7 +1826,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1494,7 +1853,7 @@
           <t>Array presets</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1521,7 +1880,7 @@
           <t>Docs / pack</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1548,7 +1907,7 @@
           <t>Archive</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1575,7 +1934,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1602,7 +1961,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1629,7 +1988,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1656,7 +2015,7 @@
           <t>Plot tools</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1683,7 +2042,7 @@
           <t>Editing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1710,7 +2069,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1737,7 +2096,7 @@
           <t>DSP / UI (PS batch)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -1764,7 +2123,7 @@
           <t>Cabinet</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1791,7 +2150,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1818,7 +2177,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1845,7 +2204,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1872,7 +2231,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1899,7 +2258,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1926,7 +2285,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1953,7 +2312,7 @@
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -1980,7 +2339,7 @@
           <t>DSP</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2007,7 +2366,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2061,7 +2420,7 @@
           <t>Windows</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2115,7 +2474,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -2160,7 +2519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2223,7 +2582,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2250,7 +2609,7 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2277,7 +2636,7 @@
           <t>Heatmap</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2304,7 +2663,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -2331,7 +2690,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2362,7 +2721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2440,7 +2799,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2467,7 +2826,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2494,7 +2853,7 @@
           <t>Theming &amp; Preferences</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2521,7 +2880,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2548,7 +2907,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2575,7 +2934,7 @@
           <t>Project Workflow</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2602,7 +2961,7 @@
           <t>Heatmap Export</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2629,7 +2988,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2656,7 +3015,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2683,7 +3042,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2710,7 +3069,7 @@
           <t>PDF Report</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2737,7 +3096,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2764,7 +3123,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2791,7 +3150,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2818,7 +3177,7 @@
           <t>Workspace / Grid / Layout</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2845,7 +3204,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2872,7 +3231,7 @@
           <t>Array Presets</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2899,7 +3258,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2926,7 +3285,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2953,7 +3312,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -2980,7 +3339,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3007,7 +3366,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3034,7 +3393,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3061,7 +3420,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3088,7 +3447,7 @@
           <t>Responsive UI</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3115,7 +3474,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3142,7 +3501,7 @@
           <t>Branding &amp; Installer</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -3169,7 +3528,7 @@
           <t>Versioning</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3196,7 +3555,7 @@
           <t>Color system</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3223,7 +3582,7 @@
           <t>Measured directivity</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3250,7 +3609,7 @@
           <t>Measurement Datasets</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3304,7 +3663,7 @@
           <t>Header</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3358,7 +3717,7 @@
           <t>Installer</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3403,7 +3762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3597,7 +3956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3816,6 +4175,261 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v1.4.0.7  -  Detailed Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28  |  Rotation handle + sketch sizes + 3D cabinet view</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Rotation handle, 5-degree snap</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Stalk and knob off the front face of selected units; drag to aim, snapping to 72 headings (0-355) with the live angle beside the knob. Hit-tested before selection so the knob never drops it. rotationDeg saved in the project (default 0); feeds Speaker::facing and re-solves the field</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Show sizes (W x H x D)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Checkbox in section 2: extension lines, arrowed dimension lines and values on each cabinet - W on the baffle edge, D on the firing axis, H called out as (vertical). One-line fallback below ~26 px; follows SI / imperial; display only</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>View in 3D</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet as a draggable solid (double-click resets), red baffle, W / H / D dimensioned on the box's own edges; painted with JUCE paths, no OpenGL; dialog sizes to content rather than full-screen</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Elevation views, height / tilt, Z / F (hidden)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>PLAN / FRONT / SIDE scale drawings, per-speaker baseHeightM and tiltDeg, zoom-to-selection (Z) and fit (F) - built but off behind UiConfig::showViewSwitcher; height / tilt still saved and loaded</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Speakers</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Plan sizes from the placement sketch</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Q21S 900 x 1000 mm (was 1546 x 1024), BEM 2inch 500 x 500 mm (was 459 x 150); heights unchanged at 679 and 276.5 mm. Near-field floor follows depth: Q21S 512 -&gt; 500 mm, horn 75 -&gt; 250 mm</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Mojibake purged</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>JUCE reads literal bytes as Latin-1, so W x H x D showed as 'W A- H A- D' and two tooltips showed 'a&lt;euro&gt;'. 246 characters across 30 files plus 34 double-encoded sequences replaced; zero non-ASCII left in Source/ string literals</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Changed</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Version -&gt; v1.4.0.7</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App, resource (string and numeric FILEVERSION, stale at 1,4,0,4), installer, archive HTML/json, Windows Release EXE</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3878,7 +4492,7 @@
           <t>Export (PNG)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3905,7 +4519,7 @@
           <t>Export (PNG)</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -3932,7 +4546,7 @@
           <t>Export</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3986,7 +4600,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4013,7 +4627,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4040,7 +4654,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4094,7 +4708,7 @@
           <t>Export</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4148,7 +4762,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4175,7 +4789,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4205,7 +4819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4268,7 +4882,7 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4295,7 +4909,7 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4322,7 +4936,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4349,7 +4963,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4376,7 +4990,7 @@
           <t>Naming</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4403,7 +5017,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4430,7 +5044,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4460,7 +5074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4523,7 +5137,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4550,7 +5164,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4577,7 +5191,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4607,7 +5221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4670,7 +5284,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -4697,7 +5311,7 @@
           <t>Engine</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4724,7 +5338,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4751,7 +5365,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4778,7 +5392,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4832,7 +5446,7 @@
           <t>Autosave</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -4859,7 +5473,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4886,7 +5500,7 @@
           <t>Sidebar</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4913,7 +5527,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4940,7 +5554,7 @@
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4967,7 +5581,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -4997,7 +5611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5060,7 +5674,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5087,7 +5701,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5114,7 +5728,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5141,7 +5755,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5168,7 +5782,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5222,7 +5836,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5249,7 +5863,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5279,7 +5893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5342,7 +5956,7 @@
           <t>Branding</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5369,7 +5983,7 @@
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5396,7 +6010,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -5423,7 +6037,7 @@
           <t>Naming</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5450,7 +6064,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5504,7 +6118,7 @@
           <t>Speakers</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5531,7 +6145,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5558,7 +6172,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5585,7 +6199,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5612,7 +6226,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5639,7 +6253,7 @@
           <t>Layout</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5666,7 +6280,7 @@
           <t>Theme</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5720,7 +6334,7 @@
           <t>Plot</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5774,7 +6388,7 @@
           <t>Measurements</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5828,7 +6442,7 @@
           <t>Help</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5882,7 +6496,7 @@
           <t>Legend</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5936,7 +6550,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5963,7 +6577,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -5993,7 +6607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6056,7 +6670,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6083,7 +6697,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6110,7 +6724,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6137,7 +6751,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6164,7 +6778,7 @@
           <t>Terminal</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
@@ -6218,7 +6832,7 @@
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Changed</t>
         </is>
@@ -6236,342 +6850,6 @@
       <c r="E11" s="6" t="inlineStr">
         <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>v1.3.7  -  Detailed Changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02  |  Gain fix + text box + clean slate + drawing UX</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Speakers</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Gain (dB) affects SPL</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Unity-gain reference normalisation; per-speaker level and array balance visible on heatmap</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Speakers</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Delete all selected</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Sidebar Delete removes every speaker in plot multi-selection, not just primary unit</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Line first stroke</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Minimum drag distance prevents accidental micro-line consuming first click</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Esc + Shape menu</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Esc returns to Select from drawing tools; cursor tool no longer opens Shape menu</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Command terminal</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Bottom-panel terminal replaces Phase/Arrival/STI placeholders; cls/clear supported</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Plot tools</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Added</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Text box annotations</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Shape menu Text Box; fill colour like shapes; rotation handle; double-click edit</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Speakers</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Delay slider max 10 ms</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Was 50 ms; presets unchanged</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Clean slate on first open</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>No default speakers until user adds a Q21S unit</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Range off by default</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Distance rings hidden until Range toggle is on</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Changed</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Version → v1.3.7 (refresh)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>App, resource, installer defines, archive HTML/json, Windows Release EXE</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/ShyamGui/CHANGELOG.xlsx
+++ b/ShyamGui/CHANGELOG.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Atomik Simulation Engine - Changelog</t>
+          <t>Atomik Integral - Changelog</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -613,366 +613,476 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.7</t>
+          <t>1.4.4</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Rotation handle + sketch sizes + 3D cabinet view</t>
+          <t>Figma icon ribbon; mouse wheel sets any number box</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>5-degree rotation handle on selected units (rotationDeg saved, re-solves the field); plan footprints from the placement sketch (Q21S 900 x 1000 mm, BEM 2inch 500 x 500 mm); Show sizes dimensions each cabinet W / D / H on the plan; View in 3D from Properties with W / H / D on the box's edges; zero non-ASCII in UI string literals (mojibake fixed); elevation views, height / tilt and Z / F shortcuts built but hidden behind a flag</t>
+          <t>Mapping ribbon drawn from the Figma icon set - Rays, Mapping Type, Options, Plane, Mic and Range - in three states: grey unavailable, black available, red on; hover shows the old button name in bold over its description; Mapping icons a third larger; status message moved into the tab strip so it shows in full; mic X / Y boxes name their axis inside the field; the mouse wheel steps any sidebar number box under the pointer (Shift for ten) and the mic X / Y boxes; new shapes light blue #A9C7FF at 100% opacity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.6</t>
+          <t>1.4.3</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Export metrics strip redesigned; Peak SPL withdrawn</t>
+          <t>Renamed Atomik Integral; mic X / Y typed in</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; exports now truly overwrite (PNG and CSV were being appended to an existing file, so the old content kept showing); /utf-8 added to both build configs, fixing the mojibake separators</t>
+          <t>Product renamed Atomik Integral across titles, reports, exports, EXE, installer and archive names; mics placed by typing X / Y in the Selected panel or ribbon; Show Values a live crosshair probe; magnifier rebuilt opaque with rim and crosshair; readability pass on axis numbers, ring labels, ribbon and FR plot; Show Rays for mids and tops only. No archive build - carried by 1.4.4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.5</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>BEM 2inch as a second speaker model</t>
+          <t>Filters reach every view; real dB SPL on both FR plots</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
+          <t>The crossover was applied inside the smoothed band sum the SPL map is built from and nowhere else, so the single-frequency pressure field, the incoherent sum and the Directivity polar were drawn from the unfiltered signal; H now multiplies the complex pressure in all of them, and is taken at the frequency being propagated rather than the browsed model's own catalogue frequency; both frequency-response displays read calibrated dB SPL on an axis anchored on first data instead of a map-relative figure re-centred every solve; the Listen window's probe was running with no directivity tables and no calibration; the view no longer snaps back to the same framing after every edit; subs carry no aiming ray; mic X / Y printed on the map with a Show Coordinates toggle; right-click &gt; Copy image to clipboard; Frequency Response window laid out from its own size</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>New Rel. SPL gradient + readable legend</t>
+          <t>Crossover filters on any cabinet (was 1.5.0)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
+          <t>Off / Low pass / High pass, Linkwitz-Riley or Butterworth, 2nd or 4th order at a corner you set, applied to the whole selection and saved with the project; the analogue prototypes evaluated at the run frequency, verified against the reference implementation over 288 combinations (largest difference 0.000e+00); H applied to the complex pressure so phase moves with level, evaluated at every smoothing sub-band; ranges can be hidden without being forgotten; mic ring snap no longer pulls on a hard-coded 1 / 2 / 4 / 8 m set that was drawn nowhere. Renumbered from 1.5.0 to keep the line on 1.4.x - same build</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>1.4.0.2</t>
+          <t>1.4.0.9</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>8-unit cap + parallel solve + autosave fixes</t>
+          <t>Mapping ribbon, planes that act, listening at a mic</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
+          <t>Home / Mapping ribbon tabs; aiming rays grabbable anywhere along their length, with Lock Rays and whole-selection turning; shapes markable as Listening, Virtual or Architectural planes, each with its own stroke, stopping rays or letting them through, reporting coverage from the solved grid and clipping the SPL map to the audience; Listening height (Seated / Standing) as documentation only; Show Values across the map; range rings at any distance typed, metric or imperial; listen at a mic with the sound following as you drag; rotation for rectangles and squares; click again to reach what is underneath; text box rebuild; MP3 loads (the build had no audio backends compiled in at all)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1.4.0.1</t>
+          <t>1.4.0.7</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>No letterboxing + pan + true Q21S size</t>
+          <t>Rotation handle + sketch sizes + 3D cabinet view</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
+          <t>5-degree rotation handle on selected units (rotationDeg saved, re-solves the field); plan footprints from the placement sketch (Q21S 900 x 1000 mm, BEM 2inch 500 x 500 mm); Show sizes dimensions each cabinet W / D / H on the plan; View in 3D from Properties with W / H / D on the box's edges; zero non-ASCII in UI string literals (mojibake fixed); elevation views, height / tilt and Z / F shortcuts built but hidden behind a flag</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.4.0.6</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Figma UI cut + square full-bleed grid</t>
+          <t>Export metrics strip redesigned; Peak SPL withdrawn</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
+          <t>Charcoal footer strip and its duplicate wordmark replaced by a labelled key/value metrics panel (Frequency, Wavelength, Devices, Directivity, Scale, Dynamic range, Grid); Peak SPL removed from PNG and PDF because the 2" horn's unit-drive BEM data was being treated as absolutely calibrated and printed beside Q21S as if comparable; exports now truly overwrite (PNG and CSV were being appended to an existing file, so the old content kept showing); /utf-8 added to both build configs, fixing the mojibake separators</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.4.0.5</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>15W750 second measurement source</t>
+          <t>BEM 2inch as a second speaker model</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
+          <t>2" BEM HF horn added alongside Q21S with per-unit model tags, so one scene can mix both and each unit is simulated from its own model's measured data; own 9-band frequency catalogue (64 - 17266 Hz), own embedded polar pack; unit names now use a space-free model tag numbered within their own model (BEM2inch_1); redundant Measurement set row removed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.4.0.4</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Command line + aliases</t>
+          <t>New Rel. SPL gradient + readable legend</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
+          <t>Six-stop Figma gradient (#FF0103 -&gt; #F65556 -&gt; #CD617C -&gt; #3281B9 -&gt; #003A6C -&gt; #151515) with the designer's uneven stop positions, giving a longer hot band; legend tick labels 18% larger</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.4.0.2</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Gain fix + text box + drawing UX</t>
+          <t>8-unit cap + parallel solve + autosave fixes</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
+          <t>Q21S units capped at 8; SPL solve across all cores (0.4s -&gt; 0.1s at 8 units); autosave timing and status corrected; Opacity readout, sizing and greying; grey sidebar outlines, larger field labels, bigger Recent Projects list</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.4.0.1</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Mic snap + shape-edge tak</t>
+          <t>No letterboxing + pan + true Q21S size</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+          <t>Fill-the-canvas fit is the zoom floor, so the plot never letterboxes; pan fixed and middle-drag pans from any tool; Q21S cabinet corrected to 1546 x 679 x 1024 mm and drawn to scale; SPL caption back at the canvas edge; lighter grid lines</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.4.0</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Mic tool + embedded Q21S Setup</t>
+          <t>Figma UI cut + square full-bleed grid</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+          <t>New ATOMIK. wordmark, ribbon, sidebar and dashboard built to measured Figma geometry; Heatmap renamed Gradient Plot; square grid cells ruled edge to edge; contrast-aware axis numbers and caption; sidebar holds its width share at any aspect; 4K scale ceiling; icon-free info panels with a close cross; v1.4.0 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.3.9</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Q21S BEM heatmap + Windows/mac product</t>
+          <t>15W750 second measurement source</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+          <t>15W750 added alongside Q21S as a fully isolated source; per-model frequency isolation so browsing one model never affects the active simulation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>1.2.x</t>
+          <t>1.3.8</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>~2026-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Beta UI redesign (betav1.2.3)</t>
+          <t>Command line + aliases</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+          <t>Command registry (short=full); typed-point DRAW; MOVE/ZOOM sessions; dock/undock terminal; Atomik HELP; Esc keeps float focused; v1.3.8 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Major feature + UX release</t>
+          <t>Gain fix + text box + drawing UX</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+          <t>Gain slider affects SPL again; sidebar Delete removes all selected speakers; text box annotations (fill + rotate); clean slate on first open; Range off by default; Esc/Line/Shape-menu fixes; command terminal; delay max 10 ms; v1.3.7 Windows Release</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>1.3.6</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Mic snap + shape-edge tak</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Restored original mic Drag::Mic ring snap; tak when drawings meet edge-to-edge; start.md for build/run; v1.3.6 Windows Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>1.3.5</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Mic tool + embedded Q21S Setup</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Virtual mics, FR floating window, Show Degrees, tak snap sound; Q21S CSVs baked into EXE; Windows Setup without Excel/Data folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Q21S BEM heatmap + Windows/mac product</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>BEM polar×1/r full-grid SPL, cardioid, Q21S 750×784×917 mm, plot tools/shapes, undo/redo, ATOMIK branding, version archive, Windows portable ZIP (EXE+Data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>1.2.x</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>~2026-07</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Beta UI redesign (betav1.2.3)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Graph colors.pdf chrome: brand tokens, heatmap colour stops, light/dark sidebar; packaged as betav1.2.3-style Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Major feature + UX release</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Theming, project dashboard/.atmk, heatmap + PDF export, grid/CAD-DXF, array presets, dual datasets, responsive window, branded installer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Initial baseline</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Dual-subwoofer (XN18) prediction &amp; visualisation in a 30x30 m world; measured directivity added 2026-06-24</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
